--- a/cases/ACDC_case24_MatACDC_24h.xlsx
+++ b/cases/ACDC_case24_MatACDC_24h.xlsx
@@ -1376,76 +1376,76 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>35.007</v>
+        <v>35.797</v>
       </c>
       <c r="C2" t="n">
-        <v>36.52</v>
+        <v>37.523</v>
       </c>
       <c r="D2" t="n">
-        <v>36.795</v>
+        <v>37.913</v>
       </c>
       <c r="E2" t="n">
-        <v>34.362</v>
+        <v>35.44</v>
       </c>
       <c r="F2" t="n">
-        <v>34.386</v>
+        <v>35.431</v>
       </c>
       <c r="G2" t="n">
-        <v>36.655</v>
+        <v>37.661</v>
       </c>
       <c r="H2" t="n">
-        <v>37.432</v>
+        <v>38.277</v>
       </c>
       <c r="I2" t="n">
-        <v>40.802</v>
+        <v>41.449</v>
       </c>
       <c r="J2" t="n">
-        <v>47.438</v>
+        <v>47.79</v>
       </c>
       <c r="K2" t="n">
-        <v>49.145</v>
+        <v>49.025</v>
       </c>
       <c r="L2" t="n">
-        <v>59.607</v>
+        <v>58.816</v>
       </c>
       <c r="M2" t="n">
-        <v>70.458</v>
+        <v>68.741</v>
       </c>
       <c r="N2" t="n">
-        <v>81.062</v>
+        <v>78.24299999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>83.801</v>
+        <v>80.166</v>
       </c>
       <c r="P2" t="n">
-        <v>75.18300000000001</v>
+        <v>71.495</v>
       </c>
       <c r="Q2" t="n">
-        <v>72.39</v>
+        <v>68.71299999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>60.587</v>
+        <v>57.698</v>
       </c>
       <c r="S2" t="n">
-        <v>53.051</v>
+        <v>50.978</v>
       </c>
       <c r="T2" t="n">
-        <v>44.779</v>
+        <v>43.628</v>
       </c>
       <c r="U2" t="n">
-        <v>39.436</v>
+        <v>39.006</v>
       </c>
       <c r="V2" t="n">
-        <v>36.295</v>
+        <v>36.336</v>
       </c>
       <c r="W2" t="n">
-        <v>34.331</v>
+        <v>34.632</v>
       </c>
       <c r="X2" t="n">
-        <v>33.54</v>
+        <v>34.002</v>
       </c>
       <c r="Y2" t="n">
-        <v>32.783</v>
+        <v>33.387</v>
       </c>
     </row>
     <row r="3">
@@ -1453,76 +1453,76 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>33.059</v>
+        <v>33.806</v>
       </c>
       <c r="C3" t="n">
-        <v>32.237</v>
+        <v>33.122</v>
       </c>
       <c r="D3" t="n">
-        <v>32.043</v>
+        <v>33.017</v>
       </c>
       <c r="E3" t="n">
-        <v>31.389</v>
+        <v>32.374</v>
       </c>
       <c r="F3" t="n">
-        <v>33.298</v>
+        <v>34.31</v>
       </c>
       <c r="G3" t="n">
-        <v>35.474</v>
+        <v>36.448</v>
       </c>
       <c r="H3" t="n">
-        <v>38.367</v>
+        <v>39.234</v>
       </c>
       <c r="I3" t="n">
-        <v>43.826</v>
+        <v>44.521</v>
       </c>
       <c r="J3" t="n">
-        <v>43.599</v>
+        <v>43.922</v>
       </c>
       <c r="K3" t="n">
-        <v>36.101</v>
+        <v>36.013</v>
       </c>
       <c r="L3" t="n">
-        <v>30.955</v>
+        <v>30.544</v>
       </c>
       <c r="M3" t="n">
-        <v>26.132</v>
+        <v>25.495</v>
       </c>
       <c r="N3" t="n">
-        <v>23.04</v>
+        <v>22.239</v>
       </c>
       <c r="O3" t="n">
-        <v>22.836</v>
+        <v>21.845</v>
       </c>
       <c r="P3" t="n">
-        <v>23.276</v>
+        <v>22.134</v>
       </c>
       <c r="Q3" t="n">
-        <v>24.786</v>
+        <v>23.528</v>
       </c>
       <c r="R3" t="n">
-        <v>27.55</v>
+        <v>26.236</v>
       </c>
       <c r="S3" t="n">
-        <v>35.647</v>
+        <v>34.254</v>
       </c>
       <c r="T3" t="n">
-        <v>44.915</v>
+        <v>43.761</v>
       </c>
       <c r="U3" t="n">
-        <v>60.673</v>
+        <v>60.013</v>
       </c>
       <c r="V3" t="n">
-        <v>62.193</v>
+        <v>62.263</v>
       </c>
       <c r="W3" t="n">
-        <v>52.353</v>
+        <v>52.812</v>
       </c>
       <c r="X3" t="n">
-        <v>43.401</v>
+        <v>43.998</v>
       </c>
       <c r="Y3" t="n">
-        <v>37.19</v>
+        <v>37.876</v>
       </c>
     </row>
     <row r="4">
@@ -1530,76 +1530,76 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>45.474</v>
+        <v>46.501</v>
       </c>
       <c r="C4" t="n">
-        <v>48.809</v>
+        <v>50.149</v>
       </c>
       <c r="D4" t="n">
-        <v>48.937</v>
+        <v>50.424</v>
       </c>
       <c r="E4" t="n">
-        <v>49.026</v>
+        <v>50.564</v>
       </c>
       <c r="F4" t="n">
-        <v>44.594</v>
+        <v>45.949</v>
       </c>
       <c r="G4" t="n">
-        <v>42.823</v>
+        <v>43.998</v>
       </c>
       <c r="H4" t="n">
-        <v>42.469</v>
+        <v>43.428</v>
       </c>
       <c r="I4" t="n">
-        <v>40.76</v>
+        <v>41.406</v>
       </c>
       <c r="J4" t="n">
-        <v>40.601</v>
+        <v>40.902</v>
       </c>
       <c r="K4" t="n">
-        <v>36.908</v>
+        <v>36.818</v>
       </c>
       <c r="L4" t="n">
-        <v>37.581</v>
+        <v>37.082</v>
       </c>
       <c r="M4" t="n">
-        <v>37.755</v>
+        <v>36.834</v>
       </c>
       <c r="N4" t="n">
-        <v>36.201</v>
+        <v>34.942</v>
       </c>
       <c r="O4" t="n">
-        <v>34.084</v>
+        <v>32.606</v>
       </c>
       <c r="P4" t="n">
-        <v>33.588</v>
+        <v>31.94</v>
       </c>
       <c r="Q4" t="n">
-        <v>33.719</v>
+        <v>32.006</v>
       </c>
       <c r="R4" t="n">
-        <v>34.282</v>
+        <v>32.647</v>
       </c>
       <c r="S4" t="n">
-        <v>33.111</v>
+        <v>31.817</v>
       </c>
       <c r="T4" t="n">
-        <v>34.985</v>
+        <v>34.086</v>
       </c>
       <c r="U4" t="n">
-        <v>38.641</v>
+        <v>38.22</v>
       </c>
       <c r="V4" t="n">
-        <v>38.938</v>
+        <v>38.982</v>
       </c>
       <c r="W4" t="n">
-        <v>40.571</v>
+        <v>40.927</v>
       </c>
       <c r="X4" t="n">
-        <v>43.617</v>
+        <v>44.218</v>
       </c>
       <c r="Y4" t="n">
-        <v>44.357</v>
+        <v>45.175</v>
       </c>
     </row>
     <row r="5">
@@ -1607,76 +1607,76 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>54.249</v>
+        <v>55.474</v>
       </c>
       <c r="C5" t="n">
-        <v>59.492</v>
+        <v>61.125</v>
       </c>
       <c r="D5" t="n">
-        <v>58.501</v>
+        <v>60.279</v>
       </c>
       <c r="E5" t="n">
-        <v>52.673</v>
+        <v>54.325</v>
       </c>
       <c r="F5" t="n">
-        <v>55.388</v>
+        <v>57.071</v>
       </c>
       <c r="G5" t="n">
-        <v>51.927</v>
+        <v>53.352</v>
       </c>
       <c r="H5" t="n">
-        <v>50.321</v>
+        <v>51.457</v>
       </c>
       <c r="I5" t="n">
-        <v>49.314</v>
+        <v>50.096</v>
       </c>
       <c r="J5" t="n">
-        <v>48.113</v>
+        <v>48.47</v>
       </c>
       <c r="K5" t="n">
-        <v>47.109</v>
+        <v>46.994</v>
       </c>
       <c r="L5" t="n">
-        <v>44.54</v>
+        <v>43.949</v>
       </c>
       <c r="M5" t="n">
-        <v>44.25</v>
+        <v>43.172</v>
       </c>
       <c r="N5" t="n">
-        <v>42.939</v>
+        <v>41.446</v>
       </c>
       <c r="O5" t="n">
-        <v>40.643</v>
+        <v>38.88</v>
       </c>
       <c r="P5" t="n">
-        <v>39.355</v>
+        <v>37.425</v>
       </c>
       <c r="Q5" t="n">
-        <v>38.471</v>
+        <v>36.518</v>
       </c>
       <c r="R5" t="n">
-        <v>38.802</v>
+        <v>36.952</v>
       </c>
       <c r="S5" t="n">
-        <v>39.632</v>
+        <v>38.083</v>
       </c>
       <c r="T5" t="n">
-        <v>41.467</v>
+        <v>40.402</v>
       </c>
       <c r="U5" t="n">
-        <v>45.229</v>
+        <v>44.736</v>
       </c>
       <c r="V5" t="n">
-        <v>46.181</v>
+        <v>46.233</v>
       </c>
       <c r="W5" t="n">
-        <v>53.462</v>
+        <v>53.931</v>
       </c>
       <c r="X5" t="n">
-        <v>52.591</v>
+        <v>53.315</v>
       </c>
       <c r="Y5" t="n">
-        <v>52.948</v>
+        <v>53.925</v>
       </c>
     </row>
     <row r="6">
@@ -1684,76 +1684,76 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>42.105</v>
+        <v>43.056</v>
       </c>
       <c r="C6" t="n">
-        <v>47.212</v>
+        <v>48.508</v>
       </c>
       <c r="D6" t="n">
-        <v>44.223</v>
+        <v>45.566</v>
       </c>
       <c r="E6" t="n">
-        <v>47.433</v>
+        <v>48.92</v>
       </c>
       <c r="F6" t="n">
-        <v>45.899</v>
+        <v>47.294</v>
       </c>
       <c r="G6" t="n">
-        <v>48.97</v>
+        <v>50.314</v>
       </c>
       <c r="H6" t="n">
-        <v>53.7</v>
+        <v>54.913</v>
       </c>
       <c r="I6" t="n">
-        <v>57.704</v>
+        <v>58.619</v>
       </c>
       <c r="J6" t="n">
-        <v>61.264</v>
+        <v>61.719</v>
       </c>
       <c r="K6" t="n">
-        <v>55.322</v>
+        <v>55.187</v>
       </c>
       <c r="L6" t="n">
-        <v>47.175</v>
+        <v>46.549</v>
       </c>
       <c r="M6" t="n">
-        <v>39.044</v>
+        <v>38.093</v>
       </c>
       <c r="N6" t="n">
-        <v>37.127</v>
+        <v>35.836</v>
       </c>
       <c r="O6" t="n">
-        <v>34.874</v>
+        <v>33.361</v>
       </c>
       <c r="P6" t="n">
-        <v>31.606</v>
+        <v>30.055</v>
       </c>
       <c r="Q6" t="n">
-        <v>36.291</v>
+        <v>34.448</v>
       </c>
       <c r="R6" t="n">
-        <v>46.171</v>
+        <v>43.969</v>
       </c>
       <c r="S6" t="n">
-        <v>54.02</v>
+        <v>51.909</v>
       </c>
       <c r="T6" t="n">
-        <v>65.90000000000001</v>
+        <v>64.206</v>
       </c>
       <c r="U6" t="n">
-        <v>90.53700000000001</v>
+        <v>89.551</v>
       </c>
       <c r="V6" t="n">
-        <v>88.74299999999999</v>
+        <v>88.843</v>
       </c>
       <c r="W6" t="n">
-        <v>75.087</v>
+        <v>75.746</v>
       </c>
       <c r="X6" t="n">
-        <v>64.548</v>
+        <v>65.43600000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>52.757</v>
+        <v>53.73</v>
       </c>
     </row>
     <row r="7">
@@ -1761,76 +1761,76 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>36.956</v>
+        <v>37.79</v>
       </c>
       <c r="C7" t="n">
-        <v>41.366</v>
+        <v>42.502</v>
       </c>
       <c r="D7" t="n">
-        <v>40.527</v>
+        <v>41.759</v>
       </c>
       <c r="E7" t="n">
-        <v>39.142</v>
+        <v>40.37</v>
       </c>
       <c r="F7" t="n">
-        <v>40.366</v>
+        <v>41.593</v>
       </c>
       <c r="G7" t="n">
-        <v>38.524</v>
+        <v>39.581</v>
       </c>
       <c r="H7" t="n">
-        <v>35.939</v>
+        <v>36.75</v>
       </c>
       <c r="I7" t="n">
-        <v>34.809</v>
+        <v>35.361</v>
       </c>
       <c r="J7" t="n">
-        <v>35.805</v>
+        <v>36.071</v>
       </c>
       <c r="K7" t="n">
-        <v>33.985</v>
+        <v>33.901</v>
       </c>
       <c r="L7" t="n">
-        <v>34.717</v>
+        <v>34.256</v>
       </c>
       <c r="M7" t="n">
-        <v>30.943</v>
+        <v>30.189</v>
       </c>
       <c r="N7" t="n">
-        <v>31.604</v>
+        <v>30.505</v>
       </c>
       <c r="O7" t="n">
-        <v>29.955</v>
+        <v>28.656</v>
       </c>
       <c r="P7" t="n">
-        <v>28.356</v>
+        <v>26.965</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.653</v>
+        <v>26.248</v>
       </c>
       <c r="R7" t="n">
-        <v>26.561</v>
+        <v>25.294</v>
       </c>
       <c r="S7" t="n">
-        <v>27.714</v>
+        <v>26.631</v>
       </c>
       <c r="T7" t="n">
-        <v>30.612</v>
+        <v>29.825</v>
       </c>
       <c r="U7" t="n">
-        <v>30.857</v>
+        <v>30.521</v>
       </c>
       <c r="V7" t="n">
-        <v>33.342</v>
+        <v>33.38</v>
       </c>
       <c r="W7" t="n">
-        <v>37.386</v>
+        <v>37.714</v>
       </c>
       <c r="X7" t="n">
-        <v>36.611</v>
+        <v>37.115</v>
       </c>
       <c r="Y7" t="n">
-        <v>39.226</v>
+        <v>39.95</v>
       </c>
     </row>
     <row r="8">
@@ -1838,76 +1838,76 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>36.825</v>
+        <v>37.657</v>
       </c>
       <c r="C8" t="n">
-        <v>40.346</v>
+        <v>41.454</v>
       </c>
       <c r="D8" t="n">
-        <v>40.431</v>
+        <v>41.66</v>
       </c>
       <c r="E8" t="n">
-        <v>37.364</v>
+        <v>38.536</v>
       </c>
       <c r="F8" t="n">
-        <v>37.81</v>
+        <v>38.959</v>
       </c>
       <c r="G8" t="n">
-        <v>33.462</v>
+        <v>34.381</v>
       </c>
       <c r="H8" t="n">
-        <v>35.762</v>
+        <v>36.57</v>
       </c>
       <c r="I8" t="n">
-        <v>35.459</v>
+        <v>36.021</v>
       </c>
       <c r="J8" t="n">
-        <v>33.221</v>
+        <v>33.468</v>
       </c>
       <c r="K8" t="n">
-        <v>32.753</v>
+        <v>32.673</v>
       </c>
       <c r="L8" t="n">
-        <v>31.029</v>
+        <v>30.617</v>
       </c>
       <c r="M8" t="n">
-        <v>30.006</v>
+        <v>29.274</v>
       </c>
       <c r="N8" t="n">
-        <v>29.228</v>
+        <v>28.212</v>
       </c>
       <c r="O8" t="n">
-        <v>28.432</v>
+        <v>27.199</v>
       </c>
       <c r="P8" t="n">
-        <v>29.022</v>
+        <v>27.598</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.701</v>
+        <v>25.345</v>
       </c>
       <c r="R8" t="n">
-        <v>25.241</v>
+        <v>24.038</v>
       </c>
       <c r="S8" t="n">
-        <v>27.32</v>
+        <v>26.252</v>
       </c>
       <c r="T8" t="n">
-        <v>27.816</v>
+        <v>27.102</v>
       </c>
       <c r="U8" t="n">
-        <v>28.989</v>
+        <v>28.673</v>
       </c>
       <c r="V8" t="n">
-        <v>31.535</v>
+        <v>31.571</v>
       </c>
       <c r="W8" t="n">
-        <v>34.317</v>
+        <v>34.618</v>
       </c>
       <c r="X8" t="n">
-        <v>34.196</v>
+        <v>34.667</v>
       </c>
       <c r="Y8" t="n">
-        <v>35.921</v>
+        <v>36.584</v>
       </c>
     </row>
   </sheetData>
@@ -12041,76 +12041,76 @@
         <v>101</v>
       </c>
       <c r="B2" t="n">
-        <v>72.41800000000001</v>
+        <v>66.648</v>
       </c>
       <c r="C2" t="n">
-        <v>71.688</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>73.828</v>
+        <v>68.465</v>
       </c>
       <c r="E2" t="n">
-        <v>74.16500000000001</v>
+        <v>68.842</v>
       </c>
       <c r="F2" t="n">
-        <v>77.75</v>
+        <v>72.102</v>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>69.35299999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>75.288</v>
+        <v>69.289</v>
       </c>
       <c r="I2" t="n">
-        <v>75.791</v>
+        <v>69.294</v>
       </c>
       <c r="J2" t="n">
-        <v>85.24299999999999</v>
+        <v>77.288</v>
       </c>
       <c r="K2" t="n">
-        <v>105.62</v>
+        <v>94.82599999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>123.327</v>
+        <v>109.52</v>
       </c>
       <c r="M2" t="n">
-        <v>161.435</v>
+        <v>141.75</v>
       </c>
       <c r="N2" t="n">
-        <v>166.036</v>
+        <v>144.236</v>
       </c>
       <c r="O2" t="n">
-        <v>173.244</v>
+        <v>149.156</v>
       </c>
       <c r="P2" t="n">
-        <v>178.991</v>
+        <v>153.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>165.106</v>
+        <v>141.049</v>
       </c>
       <c r="R2" t="n">
-        <v>139.266</v>
+        <v>119.362</v>
       </c>
       <c r="S2" t="n">
-        <v>112.157</v>
+        <v>96.996</v>
       </c>
       <c r="T2" t="n">
-        <v>83.251</v>
+        <v>73.001</v>
       </c>
       <c r="U2" t="n">
-        <v>86.46599999999999</v>
+        <v>76.97199999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>78.56999999999999</v>
+        <v>70.79300000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>69.619</v>
+        <v>63.207</v>
       </c>
       <c r="X2" t="n">
-        <v>70.166</v>
+        <v>64.01900000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>72.346</v>
+        <v>66.312</v>
       </c>
     </row>
     <row r="3">
@@ -12118,76 +12118,76 @@
         <v>102</v>
       </c>
       <c r="B3" t="n">
-        <v>123.582</v>
+        <v>113.735</v>
       </c>
       <c r="C3" t="n">
-        <v>164.634</v>
+        <v>152.237</v>
       </c>
       <c r="D3" t="n">
-        <v>175.392</v>
+        <v>162.649</v>
       </c>
       <c r="E3" t="n">
-        <v>203.145</v>
+        <v>188.566</v>
       </c>
       <c r="F3" t="n">
-        <v>198.183</v>
+        <v>183.785</v>
       </c>
       <c r="G3" t="n">
-        <v>159.955</v>
+        <v>147.911</v>
       </c>
       <c r="H3" t="n">
-        <v>117.621</v>
+        <v>108.249</v>
       </c>
       <c r="I3" t="n">
-        <v>95.354</v>
+        <v>87.179</v>
       </c>
       <c r="J3" t="n">
-        <v>79.678</v>
+        <v>72.242</v>
       </c>
       <c r="K3" t="n">
-        <v>73.075</v>
+        <v>65.607</v>
       </c>
       <c r="L3" t="n">
-        <v>67.09099999999999</v>
+        <v>59.58</v>
       </c>
       <c r="M3" t="n">
-        <v>61.273</v>
+        <v>53.801</v>
       </c>
       <c r="N3" t="n">
-        <v>59.812</v>
+        <v>51.959</v>
       </c>
       <c r="O3" t="n">
-        <v>59.732</v>
+        <v>51.426</v>
       </c>
       <c r="P3" t="n">
-        <v>62.238</v>
+        <v>53.266</v>
       </c>
       <c r="Q3" t="n">
-        <v>61.853</v>
+        <v>52.841</v>
       </c>
       <c r="R3" t="n">
-        <v>60.137</v>
+        <v>51.543</v>
       </c>
       <c r="S3" t="n">
-        <v>59.21</v>
+        <v>51.207</v>
       </c>
       <c r="T3" t="n">
-        <v>63.932</v>
+        <v>56.06</v>
       </c>
       <c r="U3" t="n">
-        <v>71.312</v>
+        <v>63.482</v>
       </c>
       <c r="V3" t="n">
-        <v>76.441</v>
+        <v>68.875</v>
       </c>
       <c r="W3" t="n">
-        <v>88.64700000000001</v>
+        <v>80.483</v>
       </c>
       <c r="X3" t="n">
-        <v>105.979</v>
+        <v>96.694</v>
       </c>
       <c r="Y3" t="n">
-        <v>129.803</v>
+        <v>118.978</v>
       </c>
     </row>
     <row r="4">
@@ -12195,76 +12195,76 @@
         <v>103</v>
       </c>
       <c r="B4" t="n">
-        <v>214.913</v>
+        <v>197.789</v>
       </c>
       <c r="C4" t="n">
-        <v>310.432</v>
+        <v>287.058</v>
       </c>
       <c r="D4" t="n">
-        <v>349.384</v>
+        <v>324</v>
       </c>
       <c r="E4" t="n">
-        <v>387.65</v>
+        <v>356.4</v>
       </c>
       <c r="F4" t="n">
-        <v>379.623</v>
+        <v>352.042</v>
       </c>
       <c r="G4" t="n">
-        <v>293.054</v>
+        <v>270.988</v>
       </c>
       <c r="H4" t="n">
-        <v>225.615</v>
+        <v>207.639</v>
       </c>
       <c r="I4" t="n">
-        <v>179.106</v>
+        <v>163.751</v>
       </c>
       <c r="J4" t="n">
-        <v>152.93</v>
+        <v>138.658</v>
       </c>
       <c r="K4" t="n">
-        <v>129.564</v>
+        <v>116.322</v>
       </c>
       <c r="L4" t="n">
-        <v>120.927</v>
+        <v>107.389</v>
       </c>
       <c r="M4" t="n">
-        <v>121.568</v>
+        <v>106.744</v>
       </c>
       <c r="N4" t="n">
-        <v>113.619</v>
+        <v>98.70099999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>109.336</v>
+        <v>94.134</v>
       </c>
       <c r="P4" t="n">
-        <v>108.597</v>
+        <v>92.943</v>
       </c>
       <c r="Q4" t="n">
-        <v>113.427</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>109.893</v>
+        <v>94.188</v>
       </c>
       <c r="S4" t="n">
-        <v>110.388</v>
+        <v>95.46599999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>119.715</v>
+        <v>104.974</v>
       </c>
       <c r="U4" t="n">
-        <v>121.173</v>
+        <v>107.868</v>
       </c>
       <c r="V4" t="n">
-        <v>139.452</v>
+        <v>125.649</v>
       </c>
       <c r="W4" t="n">
-        <v>162.152</v>
+        <v>147.218</v>
       </c>
       <c r="X4" t="n">
-        <v>176.591</v>
+        <v>161.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>245.365</v>
+        <v>224.902</v>
       </c>
     </row>
     <row r="5">
@@ -12272,76 +12272,76 @@
         <v>104</v>
       </c>
       <c r="B5" t="n">
-        <v>83.036</v>
+        <v>76.42</v>
       </c>
       <c r="C5" t="n">
-        <v>89.226</v>
+        <v>82.508</v>
       </c>
       <c r="D5" t="n">
-        <v>89.539</v>
+        <v>83.033</v>
       </c>
       <c r="E5" t="n">
-        <v>85.94799999999999</v>
+        <v>79.78</v>
       </c>
       <c r="F5" t="n">
-        <v>79.658</v>
+        <v>73.871</v>
       </c>
       <c r="G5" t="n">
-        <v>80.489</v>
+        <v>74.429</v>
       </c>
       <c r="H5" t="n">
-        <v>77.48399999999999</v>
+        <v>71.31</v>
       </c>
       <c r="I5" t="n">
-        <v>71.685</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>77.358</v>
+        <v>70.139</v>
       </c>
       <c r="K5" t="n">
-        <v>70.441</v>
+        <v>63.242</v>
       </c>
       <c r="L5" t="n">
-        <v>72.148</v>
+        <v>64.071</v>
       </c>
       <c r="M5" t="n">
-        <v>72.01300000000001</v>
+        <v>63.232</v>
       </c>
       <c r="N5" t="n">
-        <v>62.079</v>
+        <v>53.928</v>
       </c>
       <c r="O5" t="n">
-        <v>64.637</v>
+        <v>55.649</v>
       </c>
       <c r="P5" t="n">
-        <v>58.561</v>
+        <v>50.119</v>
       </c>
       <c r="Q5" t="n">
-        <v>65.69499999999999</v>
+        <v>56.123</v>
       </c>
       <c r="R5" t="n">
-        <v>60.875</v>
+        <v>52.175</v>
       </c>
       <c r="S5" t="n">
-        <v>60.491</v>
+        <v>52.314</v>
       </c>
       <c r="T5" t="n">
-        <v>63.035</v>
+        <v>55.274</v>
       </c>
       <c r="U5" t="n">
-        <v>67.071</v>
+        <v>59.707</v>
       </c>
       <c r="V5" t="n">
-        <v>70.273</v>
+        <v>63.317</v>
       </c>
       <c r="W5" t="n">
-        <v>78.825</v>
+        <v>71.565</v>
       </c>
       <c r="X5" t="n">
-        <v>80.20099999999999</v>
+        <v>73.175</v>
       </c>
       <c r="Y5" t="n">
-        <v>88.80500000000001</v>
+        <v>81.398</v>
       </c>
     </row>
     <row r="6">
@@ -12349,76 +12349,76 @@
         <v>105</v>
       </c>
       <c r="B6" t="n">
-        <v>63.553</v>
+        <v>58.49</v>
       </c>
       <c r="C6" t="n">
-        <v>60.592</v>
+        <v>56.03</v>
       </c>
       <c r="D6" t="n">
-        <v>63.539</v>
+        <v>58.922</v>
       </c>
       <c r="E6" t="n">
-        <v>60.52</v>
+        <v>56.177</v>
       </c>
       <c r="F6" t="n">
-        <v>62.719</v>
+        <v>58.162</v>
       </c>
       <c r="G6" t="n">
-        <v>66.524</v>
+        <v>61.515</v>
       </c>
       <c r="H6" t="n">
-        <v>70.874</v>
+        <v>65.227</v>
       </c>
       <c r="I6" t="n">
-        <v>74.60299999999999</v>
+        <v>68.20699999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>83.40300000000001</v>
+        <v>75.62</v>
       </c>
       <c r="K6" t="n">
-        <v>73.334</v>
+        <v>65.839</v>
       </c>
       <c r="L6" t="n">
-        <v>54.639</v>
+        <v>48.522</v>
       </c>
       <c r="M6" t="n">
-        <v>50.922</v>
+        <v>44.713</v>
       </c>
       <c r="N6" t="n">
-        <v>47.256</v>
+        <v>41.051</v>
       </c>
       <c r="O6" t="n">
-        <v>48.542</v>
+        <v>41.793</v>
       </c>
       <c r="P6" t="n">
-        <v>44.25</v>
+        <v>37.871</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.585</v>
+        <v>39.797</v>
       </c>
       <c r="R6" t="n">
-        <v>53.902</v>
+        <v>46.199</v>
       </c>
       <c r="S6" t="n">
-        <v>67.655</v>
+        <v>58.51</v>
       </c>
       <c r="T6" t="n">
-        <v>101.598</v>
+        <v>89.089</v>
       </c>
       <c r="U6" t="n">
-        <v>113.571</v>
+        <v>101.101</v>
       </c>
       <c r="V6" t="n">
-        <v>120.147</v>
+        <v>108.254</v>
       </c>
       <c r="W6" t="n">
-        <v>105.079</v>
+        <v>95.401</v>
       </c>
       <c r="X6" t="n">
-        <v>89.34</v>
+        <v>81.51300000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>63.637</v>
+        <v>58.33</v>
       </c>
     </row>
     <row r="7">
@@ -12426,76 +12426,76 @@
         <v>106</v>
       </c>
       <c r="B7" t="n">
-        <v>168.848</v>
+        <v>155.394</v>
       </c>
       <c r="C7" t="n">
-        <v>222.841</v>
+        <v>206.062</v>
       </c>
       <c r="D7" t="n">
-        <v>278.162</v>
+        <v>257.952</v>
       </c>
       <c r="E7" t="n">
-        <v>299.033</v>
+        <v>269.28</v>
       </c>
       <c r="F7" t="n">
-        <v>263.919</v>
+        <v>244.744</v>
       </c>
       <c r="G7" t="n">
-        <v>206.317</v>
+        <v>190.782</v>
       </c>
       <c r="H7" t="n">
-        <v>181.818</v>
+        <v>167.331</v>
       </c>
       <c r="I7" t="n">
-        <v>129.09</v>
+        <v>118.023</v>
       </c>
       <c r="J7" t="n">
-        <v>115.997</v>
+        <v>105.172</v>
       </c>
       <c r="K7" t="n">
-        <v>107.678</v>
+        <v>96.673</v>
       </c>
       <c r="L7" t="n">
-        <v>91.336</v>
+        <v>81.111</v>
       </c>
       <c r="M7" t="n">
-        <v>90.562</v>
+        <v>79.51900000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>92.78</v>
+        <v>80.598</v>
       </c>
       <c r="O7" t="n">
-        <v>78.02800000000001</v>
+        <v>67.179</v>
       </c>
       <c r="P7" t="n">
-        <v>83.518</v>
+        <v>71.479</v>
       </c>
       <c r="Q7" t="n">
-        <v>80.78</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>80.03100000000001</v>
+        <v>68.593</v>
       </c>
       <c r="S7" t="n">
-        <v>84.992</v>
+        <v>73.503</v>
       </c>
       <c r="T7" t="n">
-        <v>85.32299999999999</v>
+        <v>74.81699999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>94.154</v>
+        <v>83.816</v>
       </c>
       <c r="V7" t="n">
-        <v>99.715</v>
+        <v>89.845</v>
       </c>
       <c r="W7" t="n">
-        <v>126.592</v>
+        <v>114.933</v>
       </c>
       <c r="X7" t="n">
-        <v>145.924</v>
+        <v>133.14</v>
       </c>
       <c r="Y7" t="n">
-        <v>167.036</v>
+        <v>153.105</v>
       </c>
     </row>
     <row r="8">
@@ -12503,76 +12503,76 @@
         <v>107</v>
       </c>
       <c r="B8" t="n">
-        <v>172.818</v>
+        <v>159.048</v>
       </c>
       <c r="C8" t="n">
-        <v>205.97</v>
+        <v>190.461</v>
       </c>
       <c r="D8" t="n">
-        <v>246.697</v>
+        <v>228.774</v>
       </c>
       <c r="E8" t="n">
-        <v>261.835</v>
+        <v>243.043</v>
       </c>
       <c r="F8" t="n">
-        <v>249.595</v>
+        <v>231.461</v>
       </c>
       <c r="G8" t="n">
-        <v>201.107</v>
+        <v>185.964</v>
       </c>
       <c r="H8" t="n">
-        <v>163.999</v>
+        <v>150.932</v>
       </c>
       <c r="I8" t="n">
-        <v>127.039</v>
+        <v>116.148</v>
       </c>
       <c r="J8" t="n">
-        <v>103.855</v>
+        <v>94.163</v>
       </c>
       <c r="K8" t="n">
-        <v>92.91200000000001</v>
+        <v>83.417</v>
       </c>
       <c r="L8" t="n">
-        <v>91.52200000000001</v>
+        <v>81.276</v>
       </c>
       <c r="M8" t="n">
-        <v>84.97499999999999</v>
+        <v>74.614</v>
       </c>
       <c r="N8" t="n">
-        <v>81.29000000000001</v>
+        <v>70.617</v>
       </c>
       <c r="O8" t="n">
-        <v>71.20399999999999</v>
+        <v>61.303</v>
       </c>
       <c r="P8" t="n">
-        <v>73.128</v>
+        <v>62.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>74.044</v>
+        <v>63.255</v>
       </c>
       <c r="R8" t="n">
-        <v>78.303</v>
+        <v>67.11199999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>75.545</v>
+        <v>65.333</v>
       </c>
       <c r="T8" t="n">
-        <v>79.35599999999999</v>
+        <v>69.58499999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>94.764</v>
+        <v>84.35899999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>96.846</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>111.833</v>
+        <v>101.533</v>
       </c>
       <c r="X8" t="n">
-        <v>127.579</v>
+        <v>116.402</v>
       </c>
       <c r="Y8" t="n">
-        <v>153.012</v>
+        <v>140.251</v>
       </c>
     </row>
     <row r="9">
@@ -12580,76 +12580,76 @@
         <v>108</v>
       </c>
       <c r="B9" t="n">
-        <v>119.726</v>
+        <v>110.187</v>
       </c>
       <c r="C9" t="n">
-        <v>119.072</v>
+        <v>110.106</v>
       </c>
       <c r="D9" t="n">
-        <v>108.39</v>
+        <v>100.516</v>
       </c>
       <c r="E9" t="n">
-        <v>119.559</v>
+        <v>110.979</v>
       </c>
       <c r="F9" t="n">
-        <v>124.402</v>
+        <v>115.364</v>
       </c>
       <c r="G9" t="n">
-        <v>117.012</v>
+        <v>108.201</v>
       </c>
       <c r="H9" t="n">
-        <v>111.033</v>
+        <v>102.187</v>
       </c>
       <c r="I9" t="n">
-        <v>127.061</v>
+        <v>116.168</v>
       </c>
       <c r="J9" t="n">
-        <v>140.48</v>
+        <v>127.37</v>
       </c>
       <c r="K9" t="n">
-        <v>165.751</v>
+        <v>148.81</v>
       </c>
       <c r="L9" t="n">
-        <v>191.826</v>
+        <v>170.351</v>
       </c>
       <c r="M9" t="n">
-        <v>224.222</v>
+        <v>196.881</v>
       </c>
       <c r="N9" t="n">
-        <v>271.896</v>
+        <v>236.196</v>
       </c>
       <c r="O9" t="n">
-        <v>267.711</v>
+        <v>230.488</v>
       </c>
       <c r="P9" t="n">
-        <v>255.669</v>
+        <v>218.815</v>
       </c>
       <c r="Q9" t="n">
-        <v>236.912</v>
+        <v>202.392</v>
       </c>
       <c r="R9" t="n">
-        <v>209.973</v>
+        <v>179.964</v>
       </c>
       <c r="S9" t="n">
-        <v>174.119</v>
+        <v>150.582</v>
       </c>
       <c r="T9" t="n">
-        <v>148.929</v>
+        <v>130.591</v>
       </c>
       <c r="U9" t="n">
-        <v>126.726</v>
+        <v>112.811</v>
       </c>
       <c r="V9" t="n">
-        <v>125.163</v>
+        <v>112.774</v>
       </c>
       <c r="W9" t="n">
-        <v>120.331</v>
+        <v>109.249</v>
       </c>
       <c r="X9" t="n">
-        <v>112.215</v>
+        <v>102.384</v>
       </c>
       <c r="Y9" t="n">
-        <v>108.918</v>
+        <v>99.83499999999999</v>
       </c>
     </row>
     <row r="10">
@@ -12657,76 +12657,76 @@
         <v>109</v>
       </c>
       <c r="B10" t="n">
-        <v>151.842</v>
+        <v>139.744</v>
       </c>
       <c r="C10" t="n">
-        <v>146.863</v>
+        <v>135.805</v>
       </c>
       <c r="D10" t="n">
-        <v>160.43</v>
+        <v>148.774</v>
       </c>
       <c r="E10" t="n">
-        <v>159.16</v>
+        <v>147.737</v>
       </c>
       <c r="F10" t="n">
-        <v>162.398</v>
+        <v>150.599</v>
       </c>
       <c r="G10" t="n">
-        <v>163.509</v>
+        <v>151.197</v>
       </c>
       <c r="H10" t="n">
-        <v>184.1</v>
+        <v>169.431</v>
       </c>
       <c r="I10" t="n">
-        <v>201.83</v>
+        <v>184.527</v>
       </c>
       <c r="J10" t="n">
-        <v>194.998</v>
+        <v>176.801</v>
       </c>
       <c r="K10" t="n">
-        <v>182.922</v>
+        <v>164.227</v>
       </c>
       <c r="L10" t="n">
-        <v>159.156</v>
+        <v>141.338</v>
       </c>
       <c r="M10" t="n">
-        <v>122.023</v>
+        <v>107.144</v>
       </c>
       <c r="N10" t="n">
-        <v>112.271</v>
+        <v>97.53</v>
       </c>
       <c r="O10" t="n">
-        <v>118.863</v>
+        <v>102.336</v>
       </c>
       <c r="P10" t="n">
-        <v>114.537</v>
+        <v>98.027</v>
       </c>
       <c r="Q10" t="n">
-        <v>111.271</v>
+        <v>95.05800000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>132.069</v>
+        <v>113.194</v>
       </c>
       <c r="S10" t="n">
-        <v>169.779</v>
+        <v>146.829</v>
       </c>
       <c r="T10" t="n">
-        <v>218.45</v>
+        <v>191.552</v>
       </c>
       <c r="U10" t="n">
-        <v>252.536</v>
+        <v>224.808</v>
       </c>
       <c r="V10" t="n">
-        <v>301.04</v>
+        <v>271.242</v>
       </c>
       <c r="W10" t="n">
-        <v>255.209</v>
+        <v>231.703</v>
       </c>
       <c r="X10" t="n">
-        <v>203.296</v>
+        <v>185.486</v>
       </c>
       <c r="Y10" t="n">
-        <v>177.526</v>
+        <v>162.721</v>
       </c>
     </row>
     <row r="11">
@@ -12734,76 +12734,76 @@
         <v>110</v>
       </c>
       <c r="B11" t="n">
-        <v>126.752</v>
+        <v>116.653</v>
       </c>
       <c r="C11" t="n">
-        <v>132.081</v>
+        <v>122.136</v>
       </c>
       <c r="D11" t="n">
-        <v>144.141</v>
+        <v>133.669</v>
       </c>
       <c r="E11" t="n">
-        <v>145.111</v>
+        <v>134.697</v>
       </c>
       <c r="F11" t="n">
-        <v>142.078</v>
+        <v>131.756</v>
       </c>
       <c r="G11" t="n">
-        <v>139.632</v>
+        <v>129.118</v>
       </c>
       <c r="H11" t="n">
-        <v>143.778</v>
+        <v>132.322</v>
       </c>
       <c r="I11" t="n">
-        <v>149.693</v>
+        <v>136.86</v>
       </c>
       <c r="J11" t="n">
-        <v>171.813</v>
+        <v>155.779</v>
       </c>
       <c r="K11" t="n">
-        <v>191.183</v>
+        <v>171.644</v>
       </c>
       <c r="L11" t="n">
-        <v>226.456</v>
+        <v>201.104</v>
       </c>
       <c r="M11" t="n">
-        <v>267.052</v>
+        <v>234.489</v>
       </c>
       <c r="N11" t="n">
-        <v>287.855</v>
+        <v>250.06</v>
       </c>
       <c r="O11" t="n">
-        <v>313.737</v>
+        <v>270.114</v>
       </c>
       <c r="P11" t="n">
-        <v>287.007</v>
+        <v>245.636</v>
       </c>
       <c r="Q11" t="n">
-        <v>267.66</v>
+        <v>228.66</v>
       </c>
       <c r="R11" t="n">
-        <v>238.548</v>
+        <v>204.455</v>
       </c>
       <c r="S11" t="n">
-        <v>203.65</v>
+        <v>176.121</v>
       </c>
       <c r="T11" t="n">
-        <v>171.846</v>
+        <v>150.687</v>
       </c>
       <c r="U11" t="n">
-        <v>158.024</v>
+        <v>140.674</v>
       </c>
       <c r="V11" t="n">
-        <v>143.989</v>
+        <v>129.737</v>
       </c>
       <c r="W11" t="n">
-        <v>124.263</v>
+        <v>112.818</v>
       </c>
       <c r="X11" t="n">
-        <v>129.455</v>
+        <v>118.114</v>
       </c>
       <c r="Y11" t="n">
-        <v>136.576</v>
+        <v>125.186</v>
       </c>
     </row>
     <row r="12">
@@ -12965,76 +12965,76 @@
         <v>113</v>
       </c>
       <c r="B14" t="n">
-        <v>231.331</v>
+        <v>212.899</v>
       </c>
       <c r="C14" t="n">
-        <v>229.794</v>
+        <v>212.491</v>
       </c>
       <c r="D14" t="n">
-        <v>233.098</v>
+        <v>216.163</v>
       </c>
       <c r="E14" t="n">
-        <v>238.427</v>
+        <v>221.316</v>
       </c>
       <c r="F14" t="n">
-        <v>239.779</v>
+        <v>222.359</v>
       </c>
       <c r="G14" t="n">
-        <v>252.957</v>
+        <v>233.91</v>
       </c>
       <c r="H14" t="n">
-        <v>245.284</v>
+        <v>225.741</v>
       </c>
       <c r="I14" t="n">
-        <v>296.511</v>
+        <v>271.091</v>
       </c>
       <c r="J14" t="n">
-        <v>303.677</v>
+        <v>275.338</v>
       </c>
       <c r="K14" t="n">
-        <v>287.741</v>
+        <v>258.333</v>
       </c>
       <c r="L14" t="n">
-        <v>220.404</v>
+        <v>195.729</v>
       </c>
       <c r="M14" t="n">
-        <v>188.854</v>
+        <v>165.826</v>
       </c>
       <c r="N14" t="n">
-        <v>160.087</v>
+        <v>139.067</v>
       </c>
       <c r="O14" t="n">
-        <v>173.47</v>
+        <v>149.35</v>
       </c>
       <c r="P14" t="n">
-        <v>162.707</v>
+        <v>139.253</v>
       </c>
       <c r="Q14" t="n">
-        <v>172.774</v>
+        <v>147.599</v>
       </c>
       <c r="R14" t="n">
-        <v>200.232</v>
+        <v>171.615</v>
       </c>
       <c r="S14" t="n">
-        <v>251.164</v>
+        <v>217.213</v>
       </c>
       <c r="T14" t="n">
-        <v>314.36</v>
+        <v>275.653</v>
       </c>
       <c r="U14" t="n">
-        <v>425.921</v>
+        <v>379.156</v>
       </c>
       <c r="V14" t="n">
-        <v>434.417</v>
+        <v>391.418</v>
       </c>
       <c r="W14" t="n">
-        <v>421.312</v>
+        <v>382.508</v>
       </c>
       <c r="X14" t="n">
-        <v>325.236</v>
+        <v>296.743</v>
       </c>
       <c r="Y14" t="n">
-        <v>274.363</v>
+        <v>251.481</v>
       </c>
     </row>
     <row r="15">
@@ -13042,76 +13042,76 @@
         <v>114</v>
       </c>
       <c r="B15" t="n">
-        <v>161.562</v>
+        <v>148.689</v>
       </c>
       <c r="C15" t="n">
-        <v>180.721</v>
+        <v>167.114</v>
       </c>
       <c r="D15" t="n">
-        <v>179.718</v>
+        <v>166.661</v>
       </c>
       <c r="E15" t="n">
-        <v>168.709</v>
+        <v>156.601</v>
       </c>
       <c r="F15" t="n">
-        <v>171.561</v>
+        <v>159.097</v>
       </c>
       <c r="G15" t="n">
-        <v>189.259</v>
+        <v>175.008</v>
       </c>
       <c r="H15" t="n">
-        <v>181.326</v>
+        <v>166.879</v>
       </c>
       <c r="I15" t="n">
-        <v>221.292</v>
+        <v>202.321</v>
       </c>
       <c r="J15" t="n">
-        <v>234.754</v>
+        <v>212.846</v>
       </c>
       <c r="K15" t="n">
-        <v>211.442</v>
+        <v>189.832</v>
       </c>
       <c r="L15" t="n">
-        <v>170.518</v>
+        <v>151.428</v>
       </c>
       <c r="M15" t="n">
-        <v>146.147</v>
+        <v>128.327</v>
       </c>
       <c r="N15" t="n">
-        <v>125.773</v>
+        <v>109.259</v>
       </c>
       <c r="O15" t="n">
-        <v>132.436</v>
+        <v>114.022</v>
       </c>
       <c r="P15" t="n">
-        <v>126.991</v>
+        <v>108.686</v>
       </c>
       <c r="Q15" t="n">
-        <v>130.124</v>
+        <v>111.164</v>
       </c>
       <c r="R15" t="n">
-        <v>143.608</v>
+        <v>123.084</v>
       </c>
       <c r="S15" t="n">
-        <v>191.973</v>
+        <v>166.023</v>
       </c>
       <c r="T15" t="n">
-        <v>245.962</v>
+        <v>215.676</v>
       </c>
       <c r="U15" t="n">
-        <v>303.742</v>
+        <v>270.392</v>
       </c>
       <c r="V15" t="n">
-        <v>318.699</v>
+        <v>287.153</v>
       </c>
       <c r="W15" t="n">
-        <v>302.932</v>
+        <v>275.032</v>
       </c>
       <c r="X15" t="n">
-        <v>234.813</v>
+        <v>214.242</v>
       </c>
       <c r="Y15" t="n">
-        <v>189.094</v>
+        <v>173.324</v>
       </c>
     </row>
     <row r="16">
@@ -13119,76 +13119,76 @@
         <v>115</v>
       </c>
       <c r="B16" t="n">
-        <v>391.971</v>
+        <v>360.74</v>
       </c>
       <c r="C16" t="n">
-        <v>522.442</v>
+        <v>483.104</v>
       </c>
       <c r="D16" t="n">
-        <v>640.92</v>
+        <v>594.355</v>
       </c>
       <c r="E16" t="n">
-        <v>596.442</v>
+        <v>553.636</v>
       </c>
       <c r="F16" t="n">
-        <v>572.288</v>
+        <v>530.7089999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>513.3630000000001</v>
+        <v>474.708</v>
       </c>
       <c r="H16" t="n">
-        <v>398.528</v>
+        <v>366.775</v>
       </c>
       <c r="I16" t="n">
-        <v>312.973</v>
+        <v>286.142</v>
       </c>
       <c r="J16" t="n">
-        <v>264.146</v>
+        <v>239.495</v>
       </c>
       <c r="K16" t="n">
-        <v>234.387</v>
+        <v>210.432</v>
       </c>
       <c r="L16" t="n">
-        <v>217.063</v>
+        <v>192.762</v>
       </c>
       <c r="M16" t="n">
-        <v>222.911</v>
+        <v>195.731</v>
       </c>
       <c r="N16" t="n">
-        <v>194.785</v>
+        <v>169.21</v>
       </c>
       <c r="O16" t="n">
-        <v>204.067</v>
+        <v>175.693</v>
       </c>
       <c r="P16" t="n">
-        <v>196.33</v>
+        <v>168.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>185.228</v>
+        <v>158.239</v>
       </c>
       <c r="R16" t="n">
-        <v>193.569</v>
+        <v>165.904</v>
       </c>
       <c r="S16" t="n">
-        <v>191.843</v>
+        <v>165.911</v>
       </c>
       <c r="T16" t="n">
-        <v>197.244</v>
+        <v>172.957</v>
       </c>
       <c r="U16" t="n">
-        <v>220.192</v>
+        <v>196.015</v>
       </c>
       <c r="V16" t="n">
-        <v>257.684</v>
+        <v>232.178</v>
       </c>
       <c r="W16" t="n">
-        <v>280.4</v>
+        <v>254.575</v>
       </c>
       <c r="X16" t="n">
-        <v>368.339</v>
+        <v>336.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>381.826</v>
+        <v>349.982</v>
       </c>
     </row>
     <row r="17">
@@ -13196,76 +13196,76 @@
         <v>116</v>
       </c>
       <c r="B17" t="n">
-        <v>115.166</v>
+        <v>105.99</v>
       </c>
       <c r="C17" t="n">
-        <v>120.542</v>
+        <v>111.465</v>
       </c>
       <c r="D17" t="n">
-        <v>118.467</v>
+        <v>109.86</v>
       </c>
       <c r="E17" t="n">
-        <v>109.838</v>
+        <v>101.955</v>
       </c>
       <c r="F17" t="n">
-        <v>115.856</v>
+        <v>107.439</v>
       </c>
       <c r="G17" t="n">
-        <v>103.996</v>
+        <v>96.16500000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>97.086</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>103.081</v>
+        <v>94.244</v>
       </c>
       <c r="J17" t="n">
-        <v>99.38800000000001</v>
+        <v>90.113</v>
       </c>
       <c r="K17" t="n">
-        <v>97.755</v>
+        <v>87.764</v>
       </c>
       <c r="L17" t="n">
-        <v>101.885</v>
+        <v>90.47799999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>92.21299999999999</v>
+        <v>80.96899999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>86.809</v>
+        <v>75.411</v>
       </c>
       <c r="O17" t="n">
-        <v>83.40600000000001</v>
+        <v>71.809</v>
       </c>
       <c r="P17" t="n">
-        <v>80.107</v>
+        <v>68.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>79.453</v>
+        <v>67.876</v>
       </c>
       <c r="R17" t="n">
-        <v>81.685</v>
+        <v>70.011</v>
       </c>
       <c r="S17" t="n">
-        <v>81.14400000000001</v>
+        <v>70.175</v>
       </c>
       <c r="T17" t="n">
-        <v>87.443</v>
+        <v>76.676</v>
       </c>
       <c r="U17" t="n">
-        <v>96.69199999999999</v>
+        <v>86.07599999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>99.414</v>
+        <v>89.57299999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>101.381</v>
+        <v>92.04300000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>106.085</v>
+        <v>96.792</v>
       </c>
       <c r="Y17" t="n">
-        <v>113.04</v>
+        <v>103.613</v>
       </c>
     </row>
     <row r="18">
@@ -13350,76 +13350,76 @@
         <v>118</v>
       </c>
       <c r="B19" t="n">
-        <v>416.056</v>
+        <v>382.906</v>
       </c>
       <c r="C19" t="n">
-        <v>383.281</v>
+        <v>354.421</v>
       </c>
       <c r="D19" t="n">
-        <v>394.844</v>
+        <v>366.157</v>
       </c>
       <c r="E19" t="n">
-        <v>407.291</v>
+        <v>378.06</v>
       </c>
       <c r="F19" t="n">
-        <v>397.497</v>
+        <v>368.617</v>
       </c>
       <c r="G19" t="n">
-        <v>351.001</v>
+        <v>324.572</v>
       </c>
       <c r="H19" t="n">
-        <v>362.331</v>
+        <v>333.462</v>
       </c>
       <c r="I19" t="n">
-        <v>345.995</v>
+        <v>316.333</v>
       </c>
       <c r="J19" t="n">
-        <v>327.978</v>
+        <v>297.37</v>
       </c>
       <c r="K19" t="n">
-        <v>321.962</v>
+        <v>289.056</v>
       </c>
       <c r="L19" t="n">
-        <v>337.963</v>
+        <v>300.127</v>
       </c>
       <c r="M19" t="n">
-        <v>301.024</v>
+        <v>264.319</v>
       </c>
       <c r="N19" t="n">
-        <v>306.11</v>
+        <v>265.917</v>
       </c>
       <c r="O19" t="n">
-        <v>293.699</v>
+        <v>252.863</v>
       </c>
       <c r="P19" t="n">
-        <v>266.372</v>
+        <v>227.975</v>
       </c>
       <c r="Q19" t="n">
-        <v>305.463</v>
+        <v>260.954</v>
       </c>
       <c r="R19" t="n">
-        <v>279.298</v>
+        <v>239.381</v>
       </c>
       <c r="S19" t="n">
-        <v>263.59</v>
+        <v>227.959</v>
       </c>
       <c r="T19" t="n">
-        <v>296.291</v>
+        <v>259.809</v>
       </c>
       <c r="U19" t="n">
-        <v>304.042</v>
+        <v>270.659</v>
       </c>
       <c r="V19" t="n">
-        <v>328.035</v>
+        <v>295.565</v>
       </c>
       <c r="W19" t="n">
-        <v>359.838</v>
+        <v>326.696</v>
       </c>
       <c r="X19" t="n">
-        <v>368.345</v>
+        <v>336.075</v>
       </c>
       <c r="Y19" t="n">
-        <v>387.315</v>
+        <v>355.013</v>
       </c>
     </row>
     <row r="20">
@@ -13427,76 +13427,76 @@
         <v>119</v>
       </c>
       <c r="B20" t="n">
-        <v>119.081</v>
+        <v>109.593</v>
       </c>
       <c r="C20" t="n">
-        <v>118.712</v>
+        <v>109.773</v>
       </c>
       <c r="D20" t="n">
-        <v>131.19</v>
+        <v>121.659</v>
       </c>
       <c r="E20" t="n">
-        <v>128.018</v>
+        <v>118.831</v>
       </c>
       <c r="F20" t="n">
-        <v>124.08</v>
+        <v>115.065</v>
       </c>
       <c r="G20" t="n">
-        <v>131.011</v>
+        <v>121.146</v>
       </c>
       <c r="H20" t="n">
-        <v>124.56</v>
+        <v>114.635</v>
       </c>
       <c r="I20" t="n">
-        <v>127.643</v>
+        <v>116.7</v>
       </c>
       <c r="J20" t="n">
-        <v>156.569</v>
+        <v>141.958</v>
       </c>
       <c r="K20" t="n">
-        <v>166.992</v>
+        <v>149.925</v>
       </c>
       <c r="L20" t="n">
-        <v>232.382</v>
+        <v>206.366</v>
       </c>
       <c r="M20" t="n">
-        <v>247.243</v>
+        <v>217.095</v>
       </c>
       <c r="N20" t="n">
-        <v>265.584</v>
+        <v>230.713</v>
       </c>
       <c r="O20" t="n">
-        <v>307.26</v>
+        <v>264.538</v>
       </c>
       <c r="P20" t="n">
-        <v>262.781</v>
+        <v>224.902</v>
       </c>
       <c r="Q20" t="n">
-        <v>260.501</v>
+        <v>222.544</v>
       </c>
       <c r="R20" t="n">
-        <v>214.585</v>
+        <v>183.917</v>
       </c>
       <c r="S20" t="n">
-        <v>188.769</v>
+        <v>163.252</v>
       </c>
       <c r="T20" t="n">
-        <v>161.437</v>
+        <v>141.559</v>
       </c>
       <c r="U20" t="n">
-        <v>134.053</v>
+        <v>119.334</v>
       </c>
       <c r="V20" t="n">
-        <v>128.617</v>
+        <v>115.887</v>
       </c>
       <c r="W20" t="n">
-        <v>126.716</v>
+        <v>115.046</v>
       </c>
       <c r="X20" t="n">
-        <v>115.633</v>
+        <v>105.503</v>
       </c>
       <c r="Y20" t="n">
-        <v>111.838</v>
+        <v>102.511</v>
       </c>
     </row>
     <row r="21">
@@ -13504,76 +13504,76 @@
         <v>120</v>
       </c>
       <c r="B21" t="n">
-        <v>151.05</v>
+        <v>139.015</v>
       </c>
       <c r="C21" t="n">
-        <v>154.619</v>
+        <v>142.977</v>
       </c>
       <c r="D21" t="n">
-        <v>152.984</v>
+        <v>141.869</v>
       </c>
       <c r="E21" t="n">
-        <v>146.23</v>
+        <v>135.735</v>
       </c>
       <c r="F21" t="n">
-        <v>137.64</v>
+        <v>127.64</v>
       </c>
       <c r="G21" t="n">
-        <v>136.921</v>
+        <v>126.611</v>
       </c>
       <c r="H21" t="n">
-        <v>136.989</v>
+        <v>126.075</v>
       </c>
       <c r="I21" t="n">
-        <v>132.718</v>
+        <v>121.34</v>
       </c>
       <c r="J21" t="n">
-        <v>133.481</v>
+        <v>121.025</v>
       </c>
       <c r="K21" t="n">
-        <v>127.839</v>
+        <v>114.773</v>
       </c>
       <c r="L21" t="n">
-        <v>121.178</v>
+        <v>107.612</v>
       </c>
       <c r="M21" t="n">
-        <v>129.521</v>
+        <v>113.727</v>
       </c>
       <c r="N21" t="n">
-        <v>115.539</v>
+        <v>100.369</v>
       </c>
       <c r="O21" t="n">
-        <v>104.27</v>
+        <v>89.77200000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>113.315</v>
+        <v>96.98099999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>104.949</v>
+        <v>89.657</v>
       </c>
       <c r="R21" t="n">
-        <v>105.679</v>
+        <v>90.575</v>
       </c>
       <c r="S21" t="n">
-        <v>102.998</v>
+        <v>89.075</v>
       </c>
       <c r="T21" t="n">
-        <v>125.305</v>
+        <v>109.876</v>
       </c>
       <c r="U21" t="n">
-        <v>112.917</v>
+        <v>100.519</v>
       </c>
       <c r="V21" t="n">
-        <v>119.664</v>
+        <v>107.819</v>
       </c>
       <c r="W21" t="n">
-        <v>130.581</v>
+        <v>118.554</v>
       </c>
       <c r="X21" t="n">
-        <v>144.501</v>
+        <v>131.842</v>
       </c>
       <c r="Y21" t="n">
-        <v>149.475</v>
+        <v>137.009</v>
       </c>
     </row>
     <row r="22">
@@ -13889,76 +13889,76 @@
         <v>201</v>
       </c>
       <c r="B26" t="n">
-        <v>94.157</v>
+        <v>86.655</v>
       </c>
       <c r="C26" t="n">
-        <v>96.28700000000001</v>
+        <v>89.03700000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>99.09099999999999</v>
+        <v>91.892</v>
       </c>
       <c r="E26" t="n">
-        <v>92.98699999999999</v>
+        <v>86.31399999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>92.075</v>
+        <v>85.386</v>
       </c>
       <c r="G26" t="n">
-        <v>97.40600000000001</v>
+        <v>90.072</v>
       </c>
       <c r="H26" t="n">
-        <v>112.064</v>
+        <v>103.135</v>
       </c>
       <c r="I26" t="n">
-        <v>120.889</v>
+        <v>110.526</v>
       </c>
       <c r="J26" t="n">
-        <v>132.52</v>
+        <v>120.153</v>
       </c>
       <c r="K26" t="n">
-        <v>116.058</v>
+        <v>104.196</v>
       </c>
       <c r="L26" t="n">
-        <v>99.26900000000001</v>
+        <v>88.15600000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>82.236</v>
+        <v>72.208</v>
       </c>
       <c r="N26" t="n">
-        <v>71.684</v>
+        <v>62.272</v>
       </c>
       <c r="O26" t="n">
-        <v>70.453</v>
+        <v>60.657</v>
       </c>
       <c r="P26" t="n">
-        <v>65.997</v>
+        <v>56.484</v>
       </c>
       <c r="Q26" t="n">
-        <v>75.98999999999999</v>
+        <v>64.91800000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>84.45</v>
+        <v>72.38</v>
       </c>
       <c r="S26" t="n">
-        <v>99.26000000000001</v>
+        <v>85.842</v>
       </c>
       <c r="T26" t="n">
-        <v>138.921</v>
+        <v>121.816</v>
       </c>
       <c r="U26" t="n">
-        <v>169.17</v>
+        <v>150.595</v>
       </c>
       <c r="V26" t="n">
-        <v>183.585</v>
+        <v>165.413</v>
       </c>
       <c r="W26" t="n">
-        <v>161.634</v>
+        <v>146.747</v>
       </c>
       <c r="X26" t="n">
-        <v>132.26</v>
+        <v>120.673</v>
       </c>
       <c r="Y26" t="n">
-        <v>106.284</v>
+        <v>97.42</v>
       </c>
     </row>
     <row r="27">
@@ -13966,76 +13966,76 @@
         <v>202</v>
       </c>
       <c r="B27" t="n">
-        <v>116.629</v>
+        <v>107.336</v>
       </c>
       <c r="C27" t="n">
-        <v>115.943</v>
+        <v>107.213</v>
       </c>
       <c r="D27" t="n">
-        <v>111.345</v>
+        <v>103.255</v>
       </c>
       <c r="E27" t="n">
-        <v>123.199</v>
+        <v>114.357</v>
       </c>
       <c r="F27" t="n">
-        <v>105.07</v>
+        <v>97.43600000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>112.513</v>
+        <v>104.041</v>
       </c>
       <c r="H27" t="n">
-        <v>101.245</v>
+        <v>93.178</v>
       </c>
       <c r="I27" t="n">
-        <v>97.066</v>
+        <v>88.745</v>
       </c>
       <c r="J27" t="n">
-        <v>104.016</v>
+        <v>94.309</v>
       </c>
       <c r="K27" t="n">
-        <v>100.325</v>
+        <v>90.071</v>
       </c>
       <c r="L27" t="n">
-        <v>95.977</v>
+        <v>85.232</v>
       </c>
       <c r="M27" t="n">
-        <v>87.684</v>
+        <v>76.992</v>
       </c>
       <c r="N27" t="n">
-        <v>84.26300000000001</v>
+        <v>73.199</v>
       </c>
       <c r="O27" t="n">
-        <v>89.047</v>
+        <v>76.66500000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>79.848</v>
+        <v>68.33799999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>78.637</v>
+        <v>67.179</v>
       </c>
       <c r="R27" t="n">
-        <v>79.538</v>
+        <v>68.17100000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>79.419</v>
+        <v>68.684</v>
       </c>
       <c r="T27" t="n">
-        <v>80.04300000000001</v>
+        <v>70.188</v>
       </c>
       <c r="U27" t="n">
-        <v>86.375</v>
+        <v>76.89100000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>93.83799999999999</v>
+        <v>84.54900000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>100.549</v>
+        <v>91.288</v>
       </c>
       <c r="X27" t="n">
-        <v>104.709</v>
+        <v>95.535</v>
       </c>
       <c r="Y27" t="n">
-        <v>112.106</v>
+        <v>102.757</v>
       </c>
     </row>
     <row r="28">
@@ -14043,76 +14043,76 @@
         <v>203</v>
       </c>
       <c r="B28" t="n">
-        <v>111.693</v>
+        <v>102.794</v>
       </c>
       <c r="C28" t="n">
-        <v>114.748</v>
+        <v>106.108</v>
       </c>
       <c r="D28" t="n">
-        <v>132.564</v>
+        <v>122.932</v>
       </c>
       <c r="E28" t="n">
-        <v>129.539</v>
+        <v>120.242</v>
       </c>
       <c r="F28" t="n">
-        <v>127.314</v>
+        <v>118.064</v>
       </c>
       <c r="G28" t="n">
-        <v>127.046</v>
+        <v>117.48</v>
       </c>
       <c r="H28" t="n">
-        <v>123.409</v>
+        <v>113.577</v>
       </c>
       <c r="I28" t="n">
-        <v>134.546</v>
+        <v>123.012</v>
       </c>
       <c r="J28" t="n">
-        <v>146.38</v>
+        <v>132.719</v>
       </c>
       <c r="K28" t="n">
-        <v>171.204</v>
+        <v>153.706</v>
       </c>
       <c r="L28" t="n">
-        <v>220.891</v>
+        <v>196.162</v>
       </c>
       <c r="M28" t="n">
-        <v>250.913</v>
+        <v>220.318</v>
       </c>
       <c r="N28" t="n">
-        <v>285.093</v>
+        <v>247.66</v>
       </c>
       <c r="O28" t="n">
-        <v>295.604</v>
+        <v>254.502</v>
       </c>
       <c r="P28" t="n">
-        <v>309.057</v>
+        <v>264.507</v>
       </c>
       <c r="Q28" t="n">
-        <v>269.586</v>
+        <v>230.305</v>
       </c>
       <c r="R28" t="n">
-        <v>227.021</v>
+        <v>194.575</v>
       </c>
       <c r="S28" t="n">
-        <v>198.175</v>
+        <v>171.387</v>
       </c>
       <c r="T28" t="n">
-        <v>160.964</v>
+        <v>141.144</v>
       </c>
       <c r="U28" t="n">
-        <v>128.451</v>
+        <v>114.347</v>
       </c>
       <c r="V28" t="n">
-        <v>132.241</v>
+        <v>119.152</v>
       </c>
       <c r="W28" t="n">
-        <v>116.191</v>
+        <v>105.49</v>
       </c>
       <c r="X28" t="n">
-        <v>120.669</v>
+        <v>110.098</v>
       </c>
       <c r="Y28" t="n">
-        <v>116.362</v>
+        <v>106.657</v>
       </c>
     </row>
     <row r="29">
@@ -14120,76 +14120,76 @@
         <v>204</v>
       </c>
       <c r="B29" t="n">
-        <v>51.693</v>
+        <v>47.574</v>
       </c>
       <c r="C29" t="n">
-        <v>53.421</v>
+        <v>49.398</v>
       </c>
       <c r="D29" t="n">
-        <v>49.203</v>
+        <v>45.628</v>
       </c>
       <c r="E29" t="n">
-        <v>50.707</v>
+        <v>47.068</v>
       </c>
       <c r="F29" t="n">
-        <v>47.961</v>
+        <v>44.476</v>
       </c>
       <c r="G29" t="n">
-        <v>52.9</v>
+        <v>48.917</v>
       </c>
       <c r="H29" t="n">
-        <v>52.7</v>
+        <v>48.501</v>
       </c>
       <c r="I29" t="n">
-        <v>56.351</v>
+        <v>51.52</v>
       </c>
       <c r="J29" t="n">
-        <v>62.196</v>
+        <v>56.392</v>
       </c>
       <c r="K29" t="n">
-        <v>70.179</v>
+        <v>63.006</v>
       </c>
       <c r="L29" t="n">
-        <v>78.45099999999999</v>
+        <v>69.66800000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>99.13</v>
+        <v>87.042</v>
       </c>
       <c r="N29" t="n">
-        <v>114.972</v>
+        <v>99.876</v>
       </c>
       <c r="O29" t="n">
-        <v>111.611</v>
+        <v>96.092</v>
       </c>
       <c r="P29" t="n">
-        <v>119.807</v>
+        <v>102.537</v>
       </c>
       <c r="Q29" t="n">
-        <v>107.919</v>
+        <v>92.194</v>
       </c>
       <c r="R29" t="n">
-        <v>94.849</v>
+        <v>81.29300000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>80.34399999999999</v>
+        <v>69.483</v>
       </c>
       <c r="T29" t="n">
-        <v>63.81</v>
+        <v>55.953</v>
       </c>
       <c r="U29" t="n">
-        <v>58.801</v>
+        <v>52.345</v>
       </c>
       <c r="V29" t="n">
-        <v>52.137</v>
+        <v>46.976</v>
       </c>
       <c r="W29" t="n">
-        <v>53.252</v>
+        <v>48.348</v>
       </c>
       <c r="X29" t="n">
-        <v>46.081</v>
+        <v>42.044</v>
       </c>
       <c r="Y29" t="n">
-        <v>50.759</v>
+        <v>46.525</v>
       </c>
     </row>
     <row r="30">
@@ -14197,76 +14197,76 @@
         <v>205</v>
       </c>
       <c r="B30" t="n">
-        <v>80.19</v>
+        <v>73.801</v>
       </c>
       <c r="C30" t="n">
-        <v>78.923</v>
+        <v>72.98</v>
       </c>
       <c r="D30" t="n">
-        <v>80.715</v>
+        <v>74.851</v>
       </c>
       <c r="E30" t="n">
-        <v>82.179</v>
+        <v>76.28100000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>82.309</v>
+        <v>76.32899999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>77.627</v>
+        <v>71.782</v>
       </c>
       <c r="H30" t="n">
-        <v>72.06399999999999</v>
+        <v>66.32299999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>70.504</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>73.384</v>
+        <v>66.535</v>
       </c>
       <c r="K30" t="n">
-        <v>69.48999999999999</v>
+        <v>62.388</v>
       </c>
       <c r="L30" t="n">
-        <v>70.879</v>
+        <v>62.944</v>
       </c>
       <c r="M30" t="n">
-        <v>62.14</v>
+        <v>54.563</v>
       </c>
       <c r="N30" t="n">
-        <v>63.484</v>
+        <v>55.149</v>
       </c>
       <c r="O30" t="n">
-        <v>62.923</v>
+        <v>54.174</v>
       </c>
       <c r="P30" t="n">
-        <v>55.847</v>
+        <v>47.797</v>
       </c>
       <c r="Q30" t="n">
-        <v>52.647</v>
+        <v>44.976</v>
       </c>
       <c r="R30" t="n">
-        <v>58.205</v>
+        <v>49.886</v>
       </c>
       <c r="S30" t="n">
-        <v>54.874</v>
+        <v>47.456</v>
       </c>
       <c r="T30" t="n">
-        <v>60.43</v>
+        <v>52.989</v>
       </c>
       <c r="U30" t="n">
-        <v>66.452</v>
+        <v>59.156</v>
       </c>
       <c r="V30" t="n">
-        <v>67.35599999999999</v>
+        <v>60.689</v>
       </c>
       <c r="W30" t="n">
-        <v>70.791</v>
+        <v>64.271</v>
       </c>
       <c r="X30" t="n">
-        <v>74.541</v>
+        <v>68.011</v>
       </c>
       <c r="Y30" t="n">
-        <v>75.577</v>
+        <v>69.274</v>
       </c>
     </row>
     <row r="31">
@@ -14274,76 +14274,76 @@
         <v>206</v>
       </c>
       <c r="B31" t="n">
-        <v>176.007</v>
+        <v>161.983</v>
       </c>
       <c r="C31" t="n">
-        <v>221.011</v>
+        <v>204.37</v>
       </c>
       <c r="D31" t="n">
-        <v>262.909</v>
+        <v>243.808</v>
       </c>
       <c r="E31" t="n">
-        <v>288.398</v>
+        <v>267.7</v>
       </c>
       <c r="F31" t="n">
-        <v>268.278</v>
+        <v>248.787</v>
       </c>
       <c r="G31" t="n">
-        <v>222.362</v>
+        <v>205.619</v>
       </c>
       <c r="H31" t="n">
-        <v>178.773</v>
+        <v>164.529</v>
       </c>
       <c r="I31" t="n">
-        <v>133.064</v>
+        <v>121.656</v>
       </c>
       <c r="J31" t="n">
-        <v>109.429</v>
+        <v>99.217</v>
       </c>
       <c r="K31" t="n">
-        <v>107.524</v>
+        <v>96.535</v>
       </c>
       <c r="L31" t="n">
-        <v>89.45</v>
+        <v>79.43600000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>91.946</v>
+        <v>80.73399999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>90.377</v>
+        <v>78.511</v>
       </c>
       <c r="O31" t="n">
-        <v>77.982</v>
+        <v>67.139</v>
       </c>
       <c r="P31" t="n">
-        <v>88.756</v>
+        <v>75.962</v>
       </c>
       <c r="Q31" t="n">
-        <v>84.148</v>
+        <v>71.887</v>
       </c>
       <c r="R31" t="n">
-        <v>85.226</v>
+        <v>73.04600000000001</v>
       </c>
       <c r="S31" t="n">
-        <v>88.384</v>
+        <v>76.437</v>
       </c>
       <c r="T31" t="n">
-        <v>88.959</v>
+        <v>78.006</v>
       </c>
       <c r="U31" t="n">
-        <v>92.268</v>
+        <v>82.137</v>
       </c>
       <c r="V31" t="n">
-        <v>109.81</v>
+        <v>98.941</v>
       </c>
       <c r="W31" t="n">
-        <v>123.095</v>
+        <v>111.757</v>
       </c>
       <c r="X31" t="n">
-        <v>156.712</v>
+        <v>142.983</v>
       </c>
       <c r="Y31" t="n">
-        <v>161.398</v>
+        <v>147.937</v>
       </c>
     </row>
     <row r="32">
@@ -14351,76 +14351,76 @@
         <v>207</v>
       </c>
       <c r="B32" t="n">
-        <v>81.26000000000001</v>
+        <v>74.785</v>
       </c>
       <c r="C32" t="n">
-        <v>91.379</v>
+        <v>84.499</v>
       </c>
       <c r="D32" t="n">
-        <v>85.401</v>
+        <v>79.197</v>
       </c>
       <c r="E32" t="n">
-        <v>85.395</v>
+        <v>79.26600000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>92.196</v>
+        <v>85.498</v>
       </c>
       <c r="G32" t="n">
-        <v>90.009</v>
+        <v>83.232</v>
       </c>
       <c r="H32" t="n">
-        <v>87.77800000000001</v>
+        <v>80.78400000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>92.279</v>
+        <v>84.36799999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>104.165</v>
+        <v>94.444</v>
       </c>
       <c r="K32" t="n">
-        <v>118.917</v>
+        <v>106.764</v>
       </c>
       <c r="L32" t="n">
-        <v>140.807</v>
+        <v>125.043</v>
       </c>
       <c r="M32" t="n">
-        <v>159.259</v>
+        <v>139.84</v>
       </c>
       <c r="N32" t="n">
-        <v>177.899</v>
+        <v>154.541</v>
       </c>
       <c r="O32" t="n">
-        <v>200.792</v>
+        <v>172.873</v>
       </c>
       <c r="P32" t="n">
-        <v>194.184</v>
+        <v>166.193</v>
       </c>
       <c r="Q32" t="n">
-        <v>174.746</v>
+        <v>149.284</v>
       </c>
       <c r="R32" t="n">
-        <v>159.563</v>
+        <v>136.759</v>
       </c>
       <c r="S32" t="n">
-        <v>132.73</v>
+        <v>114.788</v>
       </c>
       <c r="T32" t="n">
-        <v>120.025</v>
+        <v>105.247</v>
       </c>
       <c r="U32" t="n">
-        <v>89.48699999999999</v>
+        <v>79.661</v>
       </c>
       <c r="V32" t="n">
-        <v>85.169</v>
+        <v>76.738</v>
       </c>
       <c r="W32" t="n">
-        <v>85.011</v>
+        <v>77.181</v>
       </c>
       <c r="X32" t="n">
-        <v>85.93300000000001</v>
+        <v>78.404</v>
       </c>
       <c r="Y32" t="n">
-        <v>86.56</v>
+        <v>79.34099999999999</v>
       </c>
     </row>
     <row r="33">
@@ -14428,76 +14428,76 @@
         <v>208</v>
       </c>
       <c r="B33" t="n">
-        <v>108.554</v>
+        <v>99.905</v>
       </c>
       <c r="C33" t="n">
-        <v>117.49</v>
+        <v>108.643</v>
       </c>
       <c r="D33" t="n">
-        <v>121.414</v>
+        <v>112.593</v>
       </c>
       <c r="E33" t="n">
-        <v>117.676</v>
+        <v>109.231</v>
       </c>
       <c r="F33" t="n">
-        <v>120.837</v>
+        <v>112.058</v>
       </c>
       <c r="G33" t="n">
-        <v>120.925</v>
+        <v>111.819</v>
       </c>
       <c r="H33" t="n">
-        <v>120.693</v>
+        <v>111.076</v>
       </c>
       <c r="I33" t="n">
-        <v>126.544</v>
+        <v>115.696</v>
       </c>
       <c r="J33" t="n">
-        <v>150.864</v>
+        <v>136.785</v>
       </c>
       <c r="K33" t="n">
-        <v>165.222</v>
+        <v>148.336</v>
       </c>
       <c r="L33" t="n">
-        <v>201.525</v>
+        <v>178.964</v>
       </c>
       <c r="M33" t="n">
-        <v>234.678</v>
+        <v>206.062</v>
       </c>
       <c r="N33" t="n">
-        <v>280.914</v>
+        <v>244.03</v>
       </c>
       <c r="O33" t="n">
-        <v>294.463</v>
+        <v>253.52</v>
       </c>
       <c r="P33" t="n">
-        <v>291.115</v>
+        <v>249.152</v>
       </c>
       <c r="Q33" t="n">
-        <v>252.639</v>
+        <v>215.828</v>
       </c>
       <c r="R33" t="n">
-        <v>217.304</v>
+        <v>186.247</v>
       </c>
       <c r="S33" t="n">
-        <v>181.713</v>
+        <v>157.15</v>
       </c>
       <c r="T33" t="n">
-        <v>157.528</v>
+        <v>138.131</v>
       </c>
       <c r="U33" t="n">
-        <v>127.807</v>
+        <v>113.774</v>
       </c>
       <c r="V33" t="n">
-        <v>113.846</v>
+        <v>102.577</v>
       </c>
       <c r="W33" t="n">
-        <v>117.206</v>
+        <v>106.411</v>
       </c>
       <c r="X33" t="n">
-        <v>116.849</v>
+        <v>106.612</v>
       </c>
       <c r="Y33" t="n">
-        <v>111.986</v>
+        <v>102.647</v>
       </c>
     </row>
     <row r="34">
@@ -14505,76 +14505,76 @@
         <v>209</v>
       </c>
       <c r="B34" t="n">
-        <v>216.09</v>
+        <v>198.872</v>
       </c>
       <c r="C34" t="n">
-        <v>199.791</v>
+        <v>184.748</v>
       </c>
       <c r="D34" t="n">
-        <v>209.428</v>
+        <v>194.212</v>
       </c>
       <c r="E34" t="n">
-        <v>207.558</v>
+        <v>192.662</v>
       </c>
       <c r="F34" t="n">
-        <v>188.799</v>
+        <v>175.082</v>
       </c>
       <c r="G34" t="n">
-        <v>188.566</v>
+        <v>174.367</v>
       </c>
       <c r="H34" t="n">
-        <v>192.197</v>
+        <v>176.884</v>
       </c>
       <c r="I34" t="n">
-        <v>180.354</v>
+        <v>164.892</v>
       </c>
       <c r="J34" t="n">
-        <v>180.009</v>
+        <v>163.21</v>
       </c>
       <c r="K34" t="n">
-        <v>172.635</v>
+        <v>154.991</v>
       </c>
       <c r="L34" t="n">
-        <v>170.232</v>
+        <v>151.174</v>
       </c>
       <c r="M34" t="n">
-        <v>165.097</v>
+        <v>144.966</v>
       </c>
       <c r="N34" t="n">
-        <v>150.754</v>
+        <v>130.96</v>
       </c>
       <c r="O34" t="n">
-        <v>167.465</v>
+        <v>144.18</v>
       </c>
       <c r="P34" t="n">
-        <v>150.169</v>
+        <v>128.523</v>
       </c>
       <c r="Q34" t="n">
-        <v>135.102</v>
+        <v>115.417</v>
       </c>
       <c r="R34" t="n">
-        <v>139.113</v>
+        <v>119.231</v>
       </c>
       <c r="S34" t="n">
-        <v>142.513</v>
+        <v>123.249</v>
       </c>
       <c r="T34" t="n">
-        <v>150.466</v>
+        <v>131.939</v>
       </c>
       <c r="U34" t="n">
-        <v>161.401</v>
+        <v>143.68</v>
       </c>
       <c r="V34" t="n">
-        <v>172.531</v>
+        <v>155.453</v>
       </c>
       <c r="W34" t="n">
-        <v>186.892</v>
+        <v>169.679</v>
       </c>
       <c r="X34" t="n">
-        <v>195.654</v>
+        <v>178.513</v>
       </c>
       <c r="Y34" t="n">
-        <v>186.358</v>
+        <v>170.816</v>
       </c>
     </row>
     <row r="35">
@@ -14582,76 +14582,76 @@
         <v>210</v>
       </c>
       <c r="B35" t="n">
-        <v>169.453</v>
+        <v>155.952</v>
       </c>
       <c r="C35" t="n">
-        <v>159.231</v>
+        <v>147.241</v>
       </c>
       <c r="D35" t="n">
-        <v>162.057</v>
+        <v>150.283</v>
       </c>
       <c r="E35" t="n">
-        <v>177.53</v>
+        <v>164.789</v>
       </c>
       <c r="F35" t="n">
-        <v>172.346</v>
+        <v>159.825</v>
       </c>
       <c r="G35" t="n">
-        <v>174.504</v>
+        <v>161.365</v>
       </c>
       <c r="H35" t="n">
-        <v>207.572</v>
+        <v>191.033</v>
       </c>
       <c r="I35" t="n">
-        <v>230.931</v>
+        <v>211.133</v>
       </c>
       <c r="J35" t="n">
-        <v>220.566</v>
+        <v>199.982</v>
       </c>
       <c r="K35" t="n">
-        <v>207.146</v>
+        <v>185.975</v>
       </c>
       <c r="L35" t="n">
-        <v>161.198</v>
+        <v>143.152</v>
       </c>
       <c r="M35" t="n">
-        <v>148.305</v>
+        <v>130.221</v>
       </c>
       <c r="N35" t="n">
-        <v>125.88</v>
+        <v>109.352</v>
       </c>
       <c r="O35" t="n">
-        <v>123.221</v>
+        <v>106.088</v>
       </c>
       <c r="P35" t="n">
-        <v>116.28</v>
+        <v>99.518</v>
       </c>
       <c r="Q35" t="n">
-        <v>134.369</v>
+        <v>114.791</v>
       </c>
       <c r="R35" t="n">
-        <v>147.519</v>
+        <v>126.436</v>
       </c>
       <c r="S35" t="n">
-        <v>183.77</v>
+        <v>158.929</v>
       </c>
       <c r="T35" t="n">
-        <v>238.08</v>
+        <v>208.765</v>
       </c>
       <c r="U35" t="n">
-        <v>298.573</v>
+        <v>265.791</v>
       </c>
       <c r="V35" t="n">
-        <v>341.511</v>
+        <v>307.708</v>
       </c>
       <c r="W35" t="n">
-        <v>289.491</v>
+        <v>262.828</v>
       </c>
       <c r="X35" t="n">
-        <v>243.183</v>
+        <v>221.879</v>
       </c>
       <c r="Y35" t="n">
-        <v>202.845</v>
+        <v>185.927</v>
       </c>
     </row>
     <row r="36">
@@ -14813,76 +14813,76 @@
         <v>213</v>
       </c>
       <c r="B38" t="n">
-        <v>212.585</v>
+        <v>195.647</v>
       </c>
       <c r="C38" t="n">
-        <v>218.546</v>
+        <v>202.091</v>
       </c>
       <c r="D38" t="n">
-        <v>224.27</v>
+        <v>207.976</v>
       </c>
       <c r="E38" t="n">
-        <v>240.554</v>
+        <v>223.29</v>
       </c>
       <c r="F38" t="n">
-        <v>236.596</v>
+        <v>219.407</v>
       </c>
       <c r="G38" t="n">
-        <v>239.458</v>
+        <v>221.427</v>
       </c>
       <c r="H38" t="n">
-        <v>276.284</v>
+        <v>254.271</v>
       </c>
       <c r="I38" t="n">
-        <v>306.237</v>
+        <v>279.983</v>
       </c>
       <c r="J38" t="n">
-        <v>294.797</v>
+        <v>267.286</v>
       </c>
       <c r="K38" t="n">
-        <v>264.675</v>
+        <v>237.625</v>
       </c>
       <c r="L38" t="n">
-        <v>223.064</v>
+        <v>198.092</v>
       </c>
       <c r="M38" t="n">
-        <v>193.084</v>
+        <v>169.54</v>
       </c>
       <c r="N38" t="n">
-        <v>175.201</v>
+        <v>152.197</v>
       </c>
       <c r="O38" t="n">
-        <v>171.675</v>
+        <v>147.805</v>
       </c>
       <c r="P38" t="n">
-        <v>168.187</v>
+        <v>143.943</v>
       </c>
       <c r="Q38" t="n">
-        <v>180.54</v>
+        <v>154.233</v>
       </c>
       <c r="R38" t="n">
-        <v>206.444</v>
+        <v>176.939</v>
       </c>
       <c r="S38" t="n">
-        <v>244.652</v>
+        <v>211.581</v>
       </c>
       <c r="T38" t="n">
-        <v>338.189</v>
+        <v>296.548</v>
       </c>
       <c r="U38" t="n">
-        <v>432.029</v>
+        <v>384.593</v>
       </c>
       <c r="V38" t="n">
-        <v>459.599</v>
+        <v>414.107</v>
       </c>
       <c r="W38" t="n">
-        <v>405.935</v>
+        <v>368.548</v>
       </c>
       <c r="X38" t="n">
-        <v>330.002</v>
+        <v>301.092</v>
       </c>
       <c r="Y38" t="n">
-        <v>269.781</v>
+        <v>247.281</v>
       </c>
     </row>
     <row r="39">
@@ -14890,76 +14890,76 @@
         <v>214</v>
       </c>
       <c r="B39" t="n">
-        <v>221.368</v>
+        <v>203.73</v>
       </c>
       <c r="C39" t="n">
-        <v>224.246</v>
+        <v>207.361</v>
       </c>
       <c r="D39" t="n">
-        <v>239.142</v>
+        <v>221.767</v>
       </c>
       <c r="E39" t="n">
-        <v>219.941</v>
+        <v>204.156</v>
       </c>
       <c r="F39" t="n">
-        <v>217.395</v>
+        <v>201.6</v>
       </c>
       <c r="G39" t="n">
-        <v>210.738</v>
+        <v>194.87</v>
       </c>
       <c r="H39" t="n">
-        <v>221.13</v>
+        <v>203.511</v>
       </c>
       <c r="I39" t="n">
-        <v>192.426</v>
+        <v>175.929</v>
       </c>
       <c r="J39" t="n">
-        <v>181.251</v>
+        <v>164.336</v>
       </c>
       <c r="K39" t="n">
-        <v>195.874</v>
+        <v>175.855</v>
       </c>
       <c r="L39" t="n">
-        <v>175.221</v>
+        <v>155.605</v>
       </c>
       <c r="M39" t="n">
-        <v>179.545</v>
+        <v>157.652</v>
       </c>
       <c r="N39" t="n">
-        <v>186.024</v>
+        <v>161.599</v>
       </c>
       <c r="O39" t="n">
-        <v>185.064</v>
+        <v>159.332</v>
       </c>
       <c r="P39" t="n">
-        <v>169.029</v>
+        <v>144.664</v>
       </c>
       <c r="Q39" t="n">
-        <v>155.569</v>
+        <v>132.901</v>
       </c>
       <c r="R39" t="n">
-        <v>150.61</v>
+        <v>129.085</v>
       </c>
       <c r="S39" t="n">
-        <v>157.781</v>
+        <v>136.453</v>
       </c>
       <c r="T39" t="n">
-        <v>167.928</v>
+        <v>147.251</v>
       </c>
       <c r="U39" t="n">
-        <v>196.367</v>
+        <v>174.806</v>
       </c>
       <c r="V39" t="n">
-        <v>193.622</v>
+        <v>174.457</v>
       </c>
       <c r="W39" t="n">
-        <v>204.949</v>
+        <v>186.072</v>
       </c>
       <c r="X39" t="n">
-        <v>198.436</v>
+        <v>181.052</v>
       </c>
       <c r="Y39" t="n">
-        <v>232.785</v>
+        <v>213.371</v>
       </c>
     </row>
     <row r="40">
@@ -14967,76 +14967,76 @@
         <v>215</v>
       </c>
       <c r="B40" t="n">
-        <v>394.922</v>
+        <v>363.456</v>
       </c>
       <c r="C40" t="n">
-        <v>473.054</v>
+        <v>437.434</v>
       </c>
       <c r="D40" t="n">
-        <v>635.715</v>
+        <v>589.529</v>
       </c>
       <c r="E40" t="n">
-        <v>658.475</v>
+        <v>611.217</v>
       </c>
       <c r="F40" t="n">
-        <v>624.4690000000001</v>
+        <v>579.099</v>
       </c>
       <c r="G40" t="n">
-        <v>503.252</v>
+        <v>465.358</v>
       </c>
       <c r="H40" t="n">
-        <v>380.086</v>
+        <v>349.802</v>
       </c>
       <c r="I40" t="n">
-        <v>316.906</v>
+        <v>289.738</v>
       </c>
       <c r="J40" t="n">
-        <v>250.165</v>
+        <v>226.819</v>
       </c>
       <c r="K40" t="n">
-        <v>240.728</v>
+        <v>216.125</v>
       </c>
       <c r="L40" t="n">
-        <v>222.367</v>
+        <v>197.472</v>
       </c>
       <c r="M40" t="n">
-        <v>216.15</v>
+        <v>189.793</v>
       </c>
       <c r="N40" t="n">
-        <v>203.966</v>
+        <v>177.185</v>
       </c>
       <c r="O40" t="n">
-        <v>200.531</v>
+        <v>172.648</v>
       </c>
       <c r="P40" t="n">
-        <v>191.486</v>
+        <v>163.884</v>
       </c>
       <c r="Q40" t="n">
-        <v>178.916</v>
+        <v>152.846</v>
       </c>
       <c r="R40" t="n">
-        <v>198.106</v>
+        <v>169.793</v>
       </c>
       <c r="S40" t="n">
-        <v>198.225</v>
+        <v>171.43</v>
       </c>
       <c r="T40" t="n">
-        <v>214.032</v>
+        <v>187.679</v>
       </c>
       <c r="U40" t="n">
-        <v>209.003</v>
+        <v>186.055</v>
       </c>
       <c r="V40" t="n">
-        <v>259.431</v>
+        <v>233.752</v>
       </c>
       <c r="W40" t="n">
-        <v>285.241</v>
+        <v>258.97</v>
       </c>
       <c r="X40" t="n">
-        <v>327.174</v>
+        <v>298.511</v>
       </c>
       <c r="Y40" t="n">
-        <v>395.693</v>
+        <v>362.692</v>
       </c>
     </row>
     <row r="41">
@@ -15044,76 +15044,76 @@
         <v>216</v>
       </c>
       <c r="B41" t="n">
-        <v>125.494</v>
+        <v>115.495</v>
       </c>
       <c r="C41" t="n">
-        <v>166.284</v>
+        <v>153.764</v>
       </c>
       <c r="D41" t="n">
-        <v>210.741</v>
+        <v>195.43</v>
       </c>
       <c r="E41" t="n">
-        <v>202.322</v>
+        <v>187.801</v>
       </c>
       <c r="F41" t="n">
-        <v>204.437</v>
+        <v>189.584</v>
       </c>
       <c r="G41" t="n">
-        <v>171.218</v>
+        <v>158.326</v>
       </c>
       <c r="H41" t="n">
-        <v>119.985</v>
+        <v>110.425</v>
       </c>
       <c r="I41" t="n">
-        <v>94.32299999999999</v>
+        <v>86.23699999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>85.86799999999999</v>
+        <v>77.854</v>
       </c>
       <c r="K41" t="n">
-        <v>78.37</v>
+        <v>70.36</v>
       </c>
       <c r="L41" t="n">
-        <v>71.501</v>
+        <v>63.496</v>
       </c>
       <c r="M41" t="n">
-        <v>70.58199999999999</v>
+        <v>61.976</v>
       </c>
       <c r="N41" t="n">
-        <v>64.313</v>
+        <v>55.869</v>
       </c>
       <c r="O41" t="n">
-        <v>61.609</v>
+        <v>53.043</v>
       </c>
       <c r="P41" t="n">
-        <v>61.37</v>
+        <v>52.523</v>
       </c>
       <c r="Q41" t="n">
-        <v>55.966</v>
+        <v>47.811</v>
       </c>
       <c r="R41" t="n">
-        <v>61.066</v>
+        <v>52.339</v>
       </c>
       <c r="S41" t="n">
-        <v>62.054</v>
+        <v>53.665</v>
       </c>
       <c r="T41" t="n">
-        <v>65.557</v>
+        <v>57.485</v>
       </c>
       <c r="U41" t="n">
-        <v>71.363</v>
+        <v>63.527</v>
       </c>
       <c r="V41" t="n">
-        <v>77.105</v>
+        <v>69.473</v>
       </c>
       <c r="W41" t="n">
-        <v>81.56</v>
+        <v>74.048</v>
       </c>
       <c r="X41" t="n">
-        <v>112.708</v>
+        <v>102.834</v>
       </c>
       <c r="Y41" t="n">
-        <v>119.003</v>
+        <v>109.078</v>
       </c>
     </row>
     <row r="42">
@@ -15198,76 +15198,76 @@
         <v>218</v>
       </c>
       <c r="B43" t="n">
-        <v>283.549</v>
+        <v>260.956</v>
       </c>
       <c r="C43" t="n">
-        <v>285.051</v>
+        <v>263.587</v>
       </c>
       <c r="D43" t="n">
-        <v>307.211</v>
+        <v>284.891</v>
       </c>
       <c r="E43" t="n">
-        <v>292.2</v>
+        <v>271.229</v>
       </c>
       <c r="F43" t="n">
-        <v>296.795</v>
+        <v>275.232</v>
       </c>
       <c r="G43" t="n">
-        <v>315.775</v>
+        <v>291.998</v>
       </c>
       <c r="H43" t="n">
-        <v>335.454</v>
+        <v>308.726</v>
       </c>
       <c r="I43" t="n">
-        <v>399.044</v>
+        <v>364.834</v>
       </c>
       <c r="J43" t="n">
-        <v>395.225</v>
+        <v>358.341</v>
       </c>
       <c r="K43" t="n">
-        <v>360.775</v>
+        <v>323.902</v>
       </c>
       <c r="L43" t="n">
-        <v>300.494</v>
+        <v>266.853</v>
       </c>
       <c r="M43" t="n">
-        <v>249.544</v>
+        <v>219.116</v>
       </c>
       <c r="N43" t="n">
-        <v>197.259</v>
+        <v>171.359</v>
       </c>
       <c r="O43" t="n">
-        <v>206.432</v>
+        <v>177.729</v>
       </c>
       <c r="P43" t="n">
-        <v>195.392</v>
+        <v>167.227</v>
       </c>
       <c r="Q43" t="n">
-        <v>221.954</v>
+        <v>189.613</v>
       </c>
       <c r="R43" t="n">
-        <v>246.085</v>
+        <v>210.915</v>
       </c>
       <c r="S43" t="n">
-        <v>321.418</v>
+        <v>277.97</v>
       </c>
       <c r="T43" t="n">
-        <v>443.916</v>
+        <v>389.256</v>
       </c>
       <c r="U43" t="n">
-        <v>535.845</v>
+        <v>477.01</v>
       </c>
       <c r="V43" t="n">
-        <v>563.495</v>
+        <v>507.719</v>
       </c>
       <c r="W43" t="n">
-        <v>503.391</v>
+        <v>457.027</v>
       </c>
       <c r="X43" t="n">
-        <v>401.11</v>
+        <v>365.969</v>
       </c>
       <c r="Y43" t="n">
-        <v>349.463</v>
+        <v>320.318</v>
       </c>
     </row>
     <row r="44">
@@ -15275,76 +15275,76 @@
         <v>219</v>
       </c>
       <c r="B44" t="n">
-        <v>231.882</v>
+        <v>213.406</v>
       </c>
       <c r="C44" t="n">
-        <v>301.263</v>
+        <v>278.579</v>
       </c>
       <c r="D44" t="n">
-        <v>348.343</v>
+        <v>323.035</v>
       </c>
       <c r="E44" t="n">
-        <v>398.2</v>
+        <v>358.38</v>
       </c>
       <c r="F44" t="n">
-        <v>339.994</v>
+        <v>315.293</v>
       </c>
       <c r="G44" t="n">
-        <v>321.02</v>
+        <v>296.848</v>
       </c>
       <c r="H44" t="n">
-        <v>234.573</v>
+        <v>215.883</v>
       </c>
       <c r="I44" t="n">
-        <v>178.693</v>
+        <v>163.374</v>
       </c>
       <c r="J44" t="n">
-        <v>144.9</v>
+        <v>131.378</v>
       </c>
       <c r="K44" t="n">
-        <v>139.492</v>
+        <v>125.235</v>
       </c>
       <c r="L44" t="n">
-        <v>119.414</v>
+        <v>106.045</v>
       </c>
       <c r="M44" t="n">
-        <v>130.406</v>
+        <v>114.505</v>
       </c>
       <c r="N44" t="n">
-        <v>107.318</v>
+        <v>93.227</v>
       </c>
       <c r="O44" t="n">
-        <v>121.959</v>
+        <v>105.001</v>
       </c>
       <c r="P44" t="n">
-        <v>113.921</v>
+        <v>97.499</v>
       </c>
       <c r="Q44" t="n">
-        <v>98.849</v>
+        <v>84.446</v>
       </c>
       <c r="R44" t="n">
-        <v>112.438</v>
+        <v>96.36799999999999</v>
       </c>
       <c r="S44" t="n">
-        <v>114.267</v>
+        <v>98.821</v>
       </c>
       <c r="T44" t="n">
-        <v>114.335</v>
+        <v>100.257</v>
       </c>
       <c r="U44" t="n">
-        <v>126.19</v>
+        <v>112.335</v>
       </c>
       <c r="V44" t="n">
-        <v>147.598</v>
+        <v>132.989</v>
       </c>
       <c r="W44" t="n">
-        <v>172.345</v>
+        <v>156.471</v>
       </c>
       <c r="X44" t="n">
-        <v>181.791</v>
+        <v>165.865</v>
       </c>
       <c r="Y44" t="n">
-        <v>225.258</v>
+        <v>206.471</v>
       </c>
     </row>
     <row r="45">
@@ -15352,76 +15352,76 @@
         <v>220</v>
       </c>
       <c r="B45" t="n">
-        <v>166.626</v>
+        <v>153.349</v>
       </c>
       <c r="C45" t="n">
-        <v>221.526</v>
+        <v>204.846</v>
       </c>
       <c r="D45" t="n">
-        <v>252.375</v>
+        <v>234.039</v>
       </c>
       <c r="E45" t="n">
-        <v>273.271</v>
+        <v>253.44</v>
       </c>
       <c r="F45" t="n">
-        <v>250.255</v>
+        <v>232.073</v>
       </c>
       <c r="G45" t="n">
-        <v>203.205</v>
+        <v>187.904</v>
       </c>
       <c r="H45" t="n">
-        <v>165.186</v>
+        <v>152.025</v>
       </c>
       <c r="I45" t="n">
-        <v>129.019</v>
+        <v>117.959</v>
       </c>
       <c r="J45" t="n">
-        <v>104.619</v>
+        <v>94.85599999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>97.36799999999999</v>
+        <v>87.417</v>
       </c>
       <c r="L45" t="n">
-        <v>93.56999999999999</v>
+        <v>83.095</v>
       </c>
       <c r="M45" t="n">
-        <v>90.246</v>
+        <v>79.242</v>
       </c>
       <c r="N45" t="n">
-        <v>80.26300000000001</v>
+        <v>69.72499999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>77.55200000000001</v>
+        <v>66.76900000000001</v>
       </c>
       <c r="P45" t="n">
-        <v>78.31100000000001</v>
+        <v>67.023</v>
       </c>
       <c r="Q45" t="n">
-        <v>75.886</v>
+        <v>64.82899999999999</v>
       </c>
       <c r="R45" t="n">
-        <v>77.378</v>
+        <v>66.319</v>
       </c>
       <c r="S45" t="n">
-        <v>78.461</v>
+        <v>67.855</v>
       </c>
       <c r="T45" t="n">
-        <v>82.258</v>
+        <v>72.129</v>
       </c>
       <c r="U45" t="n">
-        <v>86.361</v>
+        <v>76.879</v>
       </c>
       <c r="V45" t="n">
-        <v>104.307</v>
+        <v>93.982</v>
       </c>
       <c r="W45" t="n">
-        <v>113.859</v>
+        <v>103.373</v>
       </c>
       <c r="X45" t="n">
-        <v>146.922</v>
+        <v>134.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>165.289</v>
+        <v>151.504</v>
       </c>
     </row>
     <row r="46">
@@ -15984,76 +15984,76 @@
         <v>101</v>
       </c>
       <c r="B2" t="n">
-        <v>14.752</v>
+        <v>13.576</v>
       </c>
       <c r="C2" t="n">
-        <v>14.603</v>
+        <v>13.504</v>
       </c>
       <c r="D2" t="n">
-        <v>15.039</v>
+        <v>13.946</v>
       </c>
       <c r="E2" t="n">
-        <v>15.108</v>
+        <v>14.023</v>
       </c>
       <c r="F2" t="n">
-        <v>15.838</v>
+        <v>14.687</v>
       </c>
       <c r="G2" t="n">
-        <v>15.278</v>
+        <v>14.127</v>
       </c>
       <c r="H2" t="n">
-        <v>15.336</v>
+        <v>14.115</v>
       </c>
       <c r="I2" t="n">
-        <v>15.439</v>
+        <v>14.115</v>
       </c>
       <c r="J2" t="n">
-        <v>17.364</v>
+        <v>15.744</v>
       </c>
       <c r="K2" t="n">
-        <v>21.515</v>
+        <v>19.316</v>
       </c>
       <c r="L2" t="n">
-        <v>25.122</v>
+        <v>22.31</v>
       </c>
       <c r="M2" t="n">
-        <v>32.885</v>
+        <v>28.875</v>
       </c>
       <c r="N2" t="n">
-        <v>33.822</v>
+        <v>29.381</v>
       </c>
       <c r="O2" t="n">
-        <v>35.29</v>
+        <v>30.384</v>
       </c>
       <c r="P2" t="n">
-        <v>36.461</v>
+        <v>31.205</v>
       </c>
       <c r="Q2" t="n">
-        <v>33.633</v>
+        <v>28.732</v>
       </c>
       <c r="R2" t="n">
-        <v>28.369</v>
+        <v>24.314</v>
       </c>
       <c r="S2" t="n">
-        <v>22.847</v>
+        <v>19.758</v>
       </c>
       <c r="T2" t="n">
-        <v>16.959</v>
+        <v>14.87</v>
       </c>
       <c r="U2" t="n">
-        <v>17.613</v>
+        <v>15.679</v>
       </c>
       <c r="V2" t="n">
-        <v>16.005</v>
+        <v>14.421</v>
       </c>
       <c r="W2" t="n">
-        <v>14.182</v>
+        <v>12.876</v>
       </c>
       <c r="X2" t="n">
-        <v>14.293</v>
+        <v>13.041</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.737</v>
+        <v>13.508</v>
       </c>
     </row>
     <row r="3">
@@ -16061,76 +16061,76 @@
         <v>102</v>
       </c>
       <c r="B3" t="n">
-        <v>25.481</v>
+        <v>23.451</v>
       </c>
       <c r="C3" t="n">
-        <v>33.945</v>
+        <v>31.389</v>
       </c>
       <c r="D3" t="n">
-        <v>36.163</v>
+        <v>33.536</v>
       </c>
       <c r="E3" t="n">
-        <v>41.886</v>
+        <v>38.88</v>
       </c>
       <c r="F3" t="n">
-        <v>40.863</v>
+        <v>37.894</v>
       </c>
       <c r="G3" t="n">
-        <v>32.98</v>
+        <v>30.497</v>
       </c>
       <c r="H3" t="n">
-        <v>24.252</v>
+        <v>22.319</v>
       </c>
       <c r="I3" t="n">
-        <v>19.661</v>
+        <v>17.975</v>
       </c>
       <c r="J3" t="n">
-        <v>16.428</v>
+        <v>14.895</v>
       </c>
       <c r="K3" t="n">
-        <v>15.067</v>
+        <v>13.527</v>
       </c>
       <c r="L3" t="n">
-        <v>13.833</v>
+        <v>12.285</v>
       </c>
       <c r="M3" t="n">
-        <v>12.634</v>
+        <v>11.093</v>
       </c>
       <c r="N3" t="n">
-        <v>12.332</v>
+        <v>10.713</v>
       </c>
       <c r="O3" t="n">
-        <v>12.316</v>
+        <v>10.603</v>
       </c>
       <c r="P3" t="n">
-        <v>12.832</v>
+        <v>10.983</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.753</v>
+        <v>10.895</v>
       </c>
       <c r="R3" t="n">
-        <v>12.399</v>
+        <v>10.627</v>
       </c>
       <c r="S3" t="n">
-        <v>12.208</v>
+        <v>10.558</v>
       </c>
       <c r="T3" t="n">
-        <v>13.182</v>
+        <v>11.559</v>
       </c>
       <c r="U3" t="n">
-        <v>14.703</v>
+        <v>13.089</v>
       </c>
       <c r="V3" t="n">
-        <v>15.761</v>
+        <v>14.201</v>
       </c>
       <c r="W3" t="n">
-        <v>18.278</v>
+        <v>16.594</v>
       </c>
       <c r="X3" t="n">
-        <v>21.851</v>
+        <v>19.937</v>
       </c>
       <c r="Y3" t="n">
-        <v>26.764</v>
+        <v>24.531</v>
       </c>
     </row>
     <row r="4">
@@ -16138,76 +16138,76 @@
         <v>103</v>
       </c>
       <c r="B4" t="n">
-        <v>44.177</v>
+        <v>40.657</v>
       </c>
       <c r="C4" t="n">
-        <v>63.811</v>
+        <v>59.006</v>
       </c>
       <c r="D4" t="n">
-        <v>71.818</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>79.684</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>78.03400000000001</v>
+        <v>72.364</v>
       </c>
       <c r="G4" t="n">
-        <v>60.239</v>
+        <v>55.703</v>
       </c>
       <c r="H4" t="n">
-        <v>46.376</v>
+        <v>42.681</v>
       </c>
       <c r="I4" t="n">
-        <v>36.816</v>
+        <v>33.66</v>
       </c>
       <c r="J4" t="n">
-        <v>31.436</v>
+        <v>28.502</v>
       </c>
       <c r="K4" t="n">
-        <v>26.633</v>
+        <v>23.911</v>
       </c>
       <c r="L4" t="n">
-        <v>24.857</v>
+        <v>22.074</v>
       </c>
       <c r="M4" t="n">
-        <v>24.989</v>
+        <v>21.942</v>
       </c>
       <c r="N4" t="n">
-        <v>23.355</v>
+        <v>20.289</v>
       </c>
       <c r="O4" t="n">
-        <v>22.475</v>
+        <v>19.35</v>
       </c>
       <c r="P4" t="n">
-        <v>22.323</v>
+        <v>19.105</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.316</v>
+        <v>19.918</v>
       </c>
       <c r="R4" t="n">
-        <v>22.589</v>
+        <v>19.361</v>
       </c>
       <c r="S4" t="n">
-        <v>22.691</v>
+        <v>19.624</v>
       </c>
       <c r="T4" t="n">
-        <v>24.608</v>
+        <v>21.578</v>
       </c>
       <c r="U4" t="n">
-        <v>24.908</v>
+        <v>22.173</v>
       </c>
       <c r="V4" t="n">
-        <v>28.665</v>
+        <v>25.828</v>
       </c>
       <c r="W4" t="n">
-        <v>33.331</v>
+        <v>30.261</v>
       </c>
       <c r="X4" t="n">
-        <v>36.299</v>
+        <v>33.119</v>
       </c>
       <c r="Y4" t="n">
-        <v>50.436</v>
+        <v>46.23</v>
       </c>
     </row>
     <row r="5">
@@ -16215,76 +16215,76 @@
         <v>104</v>
       </c>
       <c r="B5" t="n">
-        <v>16.832</v>
+        <v>15.491</v>
       </c>
       <c r="C5" t="n">
-        <v>18.086</v>
+        <v>16.725</v>
       </c>
       <c r="D5" t="n">
-        <v>18.15</v>
+        <v>16.831</v>
       </c>
       <c r="E5" t="n">
-        <v>17.422</v>
+        <v>16.172</v>
       </c>
       <c r="F5" t="n">
-        <v>16.147</v>
+        <v>14.974</v>
       </c>
       <c r="G5" t="n">
-        <v>16.315</v>
+        <v>15.087</v>
       </c>
       <c r="H5" t="n">
-        <v>15.706</v>
+        <v>14.455</v>
       </c>
       <c r="I5" t="n">
-        <v>14.531</v>
+        <v>13.285</v>
       </c>
       <c r="J5" t="n">
-        <v>15.681</v>
+        <v>14.217</v>
       </c>
       <c r="K5" t="n">
-        <v>14.279</v>
+        <v>12.819</v>
       </c>
       <c r="L5" t="n">
-        <v>14.625</v>
+        <v>12.987</v>
       </c>
       <c r="M5" t="n">
-        <v>14.597</v>
+        <v>12.817</v>
       </c>
       <c r="N5" t="n">
-        <v>12.584</v>
+        <v>10.931</v>
       </c>
       <c r="O5" t="n">
-        <v>13.102</v>
+        <v>11.28</v>
       </c>
       <c r="P5" t="n">
-        <v>11.87</v>
+        <v>10.159</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.317</v>
+        <v>11.376</v>
       </c>
       <c r="R5" t="n">
-        <v>12.339</v>
+        <v>10.576</v>
       </c>
       <c r="S5" t="n">
-        <v>12.262</v>
+        <v>10.604</v>
       </c>
       <c r="T5" t="n">
-        <v>12.777</v>
+        <v>11.204</v>
       </c>
       <c r="U5" t="n">
-        <v>13.595</v>
+        <v>12.103</v>
       </c>
       <c r="V5" t="n">
-        <v>14.244</v>
+        <v>12.835</v>
       </c>
       <c r="W5" t="n">
-        <v>15.978</v>
+        <v>14.506</v>
       </c>
       <c r="X5" t="n">
-        <v>16.257</v>
+        <v>14.833</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.001</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="6">
@@ -16292,76 +16292,76 @@
         <v>105</v>
       </c>
       <c r="B6" t="n">
-        <v>12.532</v>
+        <v>11.533</v>
       </c>
       <c r="C6" t="n">
-        <v>11.948</v>
+        <v>11.048</v>
       </c>
       <c r="D6" t="n">
-        <v>12.529</v>
+        <v>11.619</v>
       </c>
       <c r="E6" t="n">
-        <v>11.934</v>
+        <v>11.077</v>
       </c>
       <c r="F6" t="n">
-        <v>12.367</v>
+        <v>11.469</v>
       </c>
       <c r="G6" t="n">
-        <v>13.117</v>
+        <v>12.13</v>
       </c>
       <c r="H6" t="n">
-        <v>13.975</v>
+        <v>12.862</v>
       </c>
       <c r="I6" t="n">
-        <v>14.71</v>
+        <v>13.449</v>
       </c>
       <c r="J6" t="n">
-        <v>16.446</v>
+        <v>14.911</v>
       </c>
       <c r="K6" t="n">
-        <v>14.46</v>
+        <v>12.982</v>
       </c>
       <c r="L6" t="n">
-        <v>10.774</v>
+        <v>9.568</v>
       </c>
       <c r="M6" t="n">
-        <v>10.041</v>
+        <v>8.817</v>
       </c>
       <c r="N6" t="n">
-        <v>9.318</v>
+        <v>8.095000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>9.571999999999999</v>
+        <v>8.241</v>
       </c>
       <c r="P6" t="n">
-        <v>8.725</v>
+        <v>7.468</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.186</v>
+        <v>7.847</v>
       </c>
       <c r="R6" t="n">
-        <v>10.629</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>13.34</v>
+        <v>11.537</v>
       </c>
       <c r="T6" t="n">
-        <v>20.033</v>
+        <v>17.567</v>
       </c>
       <c r="U6" t="n">
-        <v>22.394</v>
+        <v>19.935</v>
       </c>
       <c r="V6" t="n">
-        <v>23.691</v>
+        <v>21.346</v>
       </c>
       <c r="W6" t="n">
-        <v>20.72</v>
+        <v>18.811</v>
       </c>
       <c r="X6" t="n">
-        <v>17.616</v>
+        <v>16.073</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.548</v>
+        <v>11.502</v>
       </c>
     </row>
     <row r="7">
@@ -16369,76 +16369,76 @@
         <v>106</v>
       </c>
       <c r="B7" t="n">
-        <v>34.763</v>
+        <v>31.993</v>
       </c>
       <c r="C7" t="n">
-        <v>45.879</v>
+        <v>42.425</v>
       </c>
       <c r="D7" t="n">
-        <v>57.269</v>
+        <v>53.108</v>
       </c>
       <c r="E7" t="n">
-        <v>61.566</v>
+        <v>55.44</v>
       </c>
       <c r="F7" t="n">
-        <v>54.336</v>
+        <v>50.389</v>
       </c>
       <c r="G7" t="n">
-        <v>42.477</v>
+        <v>39.279</v>
       </c>
       <c r="H7" t="n">
-        <v>37.433</v>
+        <v>34.451</v>
       </c>
       <c r="I7" t="n">
-        <v>26.577</v>
+        <v>24.299</v>
       </c>
       <c r="J7" t="n">
-        <v>23.882</v>
+        <v>21.653</v>
       </c>
       <c r="K7" t="n">
-        <v>22.169</v>
+        <v>19.903</v>
       </c>
       <c r="L7" t="n">
-        <v>18.804</v>
+        <v>16.699</v>
       </c>
       <c r="M7" t="n">
-        <v>18.645</v>
+        <v>16.372</v>
       </c>
       <c r="N7" t="n">
-        <v>19.102</v>
+        <v>16.594</v>
       </c>
       <c r="O7" t="n">
-        <v>16.065</v>
+        <v>13.831</v>
       </c>
       <c r="P7" t="n">
-        <v>17.195</v>
+        <v>14.716</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.631</v>
+        <v>14.208</v>
       </c>
       <c r="R7" t="n">
-        <v>16.477</v>
+        <v>14.122</v>
       </c>
       <c r="S7" t="n">
-        <v>17.498</v>
+        <v>15.133</v>
       </c>
       <c r="T7" t="n">
-        <v>17.567</v>
+        <v>15.404</v>
       </c>
       <c r="U7" t="n">
-        <v>19.385</v>
+        <v>17.256</v>
       </c>
       <c r="V7" t="n">
-        <v>20.529</v>
+        <v>18.497</v>
       </c>
       <c r="W7" t="n">
-        <v>26.063</v>
+        <v>23.663</v>
       </c>
       <c r="X7" t="n">
-        <v>30.043</v>
+        <v>27.411</v>
       </c>
       <c r="Y7" t="n">
-        <v>34.39</v>
+        <v>31.522</v>
       </c>
     </row>
     <row r="8">
@@ -16446,76 +16446,76 @@
         <v>107</v>
       </c>
       <c r="B8" t="n">
-        <v>34.564</v>
+        <v>31.81</v>
       </c>
       <c r="C8" t="n">
-        <v>41.194</v>
+        <v>38.092</v>
       </c>
       <c r="D8" t="n">
-        <v>49.339</v>
+        <v>45.755</v>
       </c>
       <c r="E8" t="n">
-        <v>52.367</v>
+        <v>48.609</v>
       </c>
       <c r="F8" t="n">
-        <v>49.919</v>
+        <v>46.292</v>
       </c>
       <c r="G8" t="n">
-        <v>40.221</v>
+        <v>37.193</v>
       </c>
       <c r="H8" t="n">
-        <v>32.8</v>
+        <v>30.186</v>
       </c>
       <c r="I8" t="n">
-        <v>25.408</v>
+        <v>23.23</v>
       </c>
       <c r="J8" t="n">
-        <v>20.771</v>
+        <v>18.833</v>
       </c>
       <c r="K8" t="n">
-        <v>18.582</v>
+        <v>16.683</v>
       </c>
       <c r="L8" t="n">
-        <v>18.304</v>
+        <v>16.255</v>
       </c>
       <c r="M8" t="n">
-        <v>16.995</v>
+        <v>14.923</v>
       </c>
       <c r="N8" t="n">
-        <v>16.258</v>
+        <v>14.123</v>
       </c>
       <c r="O8" t="n">
-        <v>14.241</v>
+        <v>12.261</v>
       </c>
       <c r="P8" t="n">
-        <v>14.626</v>
+        <v>12.517</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.809</v>
+        <v>12.651</v>
       </c>
       <c r="R8" t="n">
-        <v>15.661</v>
+        <v>13.422</v>
       </c>
       <c r="S8" t="n">
-        <v>15.109</v>
+        <v>13.067</v>
       </c>
       <c r="T8" t="n">
-        <v>15.871</v>
+        <v>13.917</v>
       </c>
       <c r="U8" t="n">
-        <v>18.953</v>
+        <v>16.872</v>
       </c>
       <c r="V8" t="n">
-        <v>19.369</v>
+        <v>17.452</v>
       </c>
       <c r="W8" t="n">
-        <v>22.367</v>
+        <v>20.307</v>
       </c>
       <c r="X8" t="n">
-        <v>25.516</v>
+        <v>23.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>30.602</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="9">
@@ -16523,76 +16523,76 @@
         <v>108</v>
       </c>
       <c r="B9" t="n">
-        <v>24.505</v>
+        <v>22.553</v>
       </c>
       <c r="C9" t="n">
-        <v>24.371</v>
+        <v>22.536</v>
       </c>
       <c r="D9" t="n">
-        <v>22.185</v>
+        <v>20.573</v>
       </c>
       <c r="E9" t="n">
-        <v>24.471</v>
+        <v>22.715</v>
       </c>
       <c r="F9" t="n">
-        <v>25.462</v>
+        <v>23.612</v>
       </c>
       <c r="G9" t="n">
-        <v>23.95</v>
+        <v>22.146</v>
       </c>
       <c r="H9" t="n">
-        <v>22.726</v>
+        <v>20.915</v>
       </c>
       <c r="I9" t="n">
-        <v>26.007</v>
+        <v>23.777</v>
       </c>
       <c r="J9" t="n">
-        <v>28.753</v>
+        <v>26.07</v>
       </c>
       <c r="K9" t="n">
-        <v>33.926</v>
+        <v>30.458</v>
       </c>
       <c r="L9" t="n">
-        <v>39.263</v>
+        <v>34.867</v>
       </c>
       <c r="M9" t="n">
-        <v>45.893</v>
+        <v>40.297</v>
       </c>
       <c r="N9" t="n">
-        <v>55.651</v>
+        <v>48.344</v>
       </c>
       <c r="O9" t="n">
-        <v>54.795</v>
+        <v>47.176</v>
       </c>
       <c r="P9" t="n">
-        <v>52.33</v>
+        <v>44.787</v>
       </c>
       <c r="Q9" t="n">
-        <v>48.491</v>
+        <v>41.425</v>
       </c>
       <c r="R9" t="n">
-        <v>42.977</v>
+        <v>36.835</v>
       </c>
       <c r="S9" t="n">
-        <v>35.638</v>
+        <v>30.821</v>
       </c>
       <c r="T9" t="n">
-        <v>30.483</v>
+        <v>26.729</v>
       </c>
       <c r="U9" t="n">
-        <v>25.938</v>
+        <v>23.09</v>
       </c>
       <c r="V9" t="n">
-        <v>25.618</v>
+        <v>23.082</v>
       </c>
       <c r="W9" t="n">
-        <v>24.629</v>
+        <v>22.361</v>
       </c>
       <c r="X9" t="n">
-        <v>22.968</v>
+        <v>20.956</v>
       </c>
       <c r="Y9" t="n">
-        <v>22.293</v>
+        <v>20.434</v>
       </c>
     </row>
     <row r="10">
@@ -16600,76 +16600,76 @@
         <v>109</v>
       </c>
       <c r="B10" t="n">
-        <v>31.236</v>
+        <v>28.747</v>
       </c>
       <c r="C10" t="n">
-        <v>30.212</v>
+        <v>27.937</v>
       </c>
       <c r="D10" t="n">
-        <v>33.003</v>
+        <v>30.605</v>
       </c>
       <c r="E10" t="n">
-        <v>32.741</v>
+        <v>30.392</v>
       </c>
       <c r="F10" t="n">
-        <v>33.408</v>
+        <v>30.98</v>
       </c>
       <c r="G10" t="n">
-        <v>33.636</v>
+        <v>31.103</v>
       </c>
       <c r="H10" t="n">
-        <v>37.872</v>
+        <v>34.854</v>
       </c>
       <c r="I10" t="n">
-        <v>41.519</v>
+        <v>37.96</v>
       </c>
       <c r="J10" t="n">
-        <v>40.114</v>
+        <v>36.37</v>
       </c>
       <c r="K10" t="n">
-        <v>37.63</v>
+        <v>33.784</v>
       </c>
       <c r="L10" t="n">
-        <v>32.741</v>
+        <v>29.075</v>
       </c>
       <c r="M10" t="n">
-        <v>25.102</v>
+        <v>22.041</v>
       </c>
       <c r="N10" t="n">
-        <v>23.096</v>
+        <v>20.063</v>
       </c>
       <c r="O10" t="n">
-        <v>24.452</v>
+        <v>21.052</v>
       </c>
       <c r="P10" t="n">
-        <v>23.562</v>
+        <v>20.166</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.89</v>
+        <v>19.555</v>
       </c>
       <c r="R10" t="n">
-        <v>27.168</v>
+        <v>23.286</v>
       </c>
       <c r="S10" t="n">
-        <v>34.926</v>
+        <v>30.205</v>
       </c>
       <c r="T10" t="n">
-        <v>44.938</v>
+        <v>39.405</v>
       </c>
       <c r="U10" t="n">
-        <v>51.95</v>
+        <v>46.246</v>
       </c>
       <c r="V10" t="n">
-        <v>61.928</v>
+        <v>55.798</v>
       </c>
       <c r="W10" t="n">
-        <v>52.5</v>
+        <v>47.665</v>
       </c>
       <c r="X10" t="n">
-        <v>41.821</v>
+        <v>38.157</v>
       </c>
       <c r="Y10" t="n">
-        <v>36.52</v>
+        <v>33.474</v>
       </c>
     </row>
     <row r="11">
@@ -16677,76 +16677,76 @@
         <v>110</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>23.929</v>
       </c>
       <c r="C11" t="n">
-        <v>27.094</v>
+        <v>25.053</v>
       </c>
       <c r="D11" t="n">
-        <v>29.567</v>
+        <v>27.419</v>
       </c>
       <c r="E11" t="n">
-        <v>29.766</v>
+        <v>27.63</v>
       </c>
       <c r="F11" t="n">
-        <v>29.144</v>
+        <v>27.027</v>
       </c>
       <c r="G11" t="n">
-        <v>28.643</v>
+        <v>26.486</v>
       </c>
       <c r="H11" t="n">
-        <v>29.493</v>
+        <v>27.143</v>
       </c>
       <c r="I11" t="n">
-        <v>30.706</v>
+        <v>28.074</v>
       </c>
       <c r="J11" t="n">
-        <v>35.244</v>
+        <v>31.955</v>
       </c>
       <c r="K11" t="n">
-        <v>39.217</v>
+        <v>35.209</v>
       </c>
       <c r="L11" t="n">
-        <v>46.453</v>
+        <v>41.252</v>
       </c>
       <c r="M11" t="n">
-        <v>54.78</v>
+        <v>48.1</v>
       </c>
       <c r="N11" t="n">
-        <v>59.047</v>
+        <v>51.294</v>
       </c>
       <c r="O11" t="n">
-        <v>64.35599999999999</v>
+        <v>55.408</v>
       </c>
       <c r="P11" t="n">
-        <v>58.873</v>
+        <v>50.387</v>
       </c>
       <c r="Q11" t="n">
-        <v>54.905</v>
+        <v>46.905</v>
       </c>
       <c r="R11" t="n">
-        <v>48.933</v>
+        <v>41.94</v>
       </c>
       <c r="S11" t="n">
-        <v>41.774</v>
+        <v>36.127</v>
       </c>
       <c r="T11" t="n">
-        <v>35.251</v>
+        <v>30.91</v>
       </c>
       <c r="U11" t="n">
-        <v>32.415</v>
+        <v>28.856</v>
       </c>
       <c r="V11" t="n">
-        <v>29.536</v>
+        <v>26.613</v>
       </c>
       <c r="W11" t="n">
-        <v>25.49</v>
+        <v>23.142</v>
       </c>
       <c r="X11" t="n">
-        <v>26.555</v>
+        <v>24.228</v>
       </c>
       <c r="Y11" t="n">
-        <v>28.016</v>
+        <v>25.679</v>
       </c>
     </row>
     <row r="12">
@@ -16908,76 +16908,76 @@
         <v>113</v>
       </c>
       <c r="B14" t="n">
-        <v>47.139</v>
+        <v>43.383</v>
       </c>
       <c r="C14" t="n">
-        <v>46.826</v>
+        <v>43.3</v>
       </c>
       <c r="D14" t="n">
-        <v>47.499</v>
+        <v>44.048</v>
       </c>
       <c r="E14" t="n">
-        <v>48.585</v>
+        <v>45.098</v>
       </c>
       <c r="F14" t="n">
-        <v>48.861</v>
+        <v>45.311</v>
       </c>
       <c r="G14" t="n">
-        <v>51.546</v>
+        <v>47.665</v>
       </c>
       <c r="H14" t="n">
-        <v>49.982</v>
+        <v>46</v>
       </c>
       <c r="I14" t="n">
-        <v>60.421</v>
+        <v>55.241</v>
       </c>
       <c r="J14" t="n">
-        <v>61.881</v>
+        <v>56.107</v>
       </c>
       <c r="K14" t="n">
-        <v>58.634</v>
+        <v>52.641</v>
       </c>
       <c r="L14" t="n">
-        <v>44.913</v>
+        <v>39.884</v>
       </c>
       <c r="M14" t="n">
-        <v>38.484</v>
+        <v>33.791</v>
       </c>
       <c r="N14" t="n">
-        <v>32.621</v>
+        <v>28.338</v>
       </c>
       <c r="O14" t="n">
-        <v>35.349</v>
+        <v>30.434</v>
       </c>
       <c r="P14" t="n">
-        <v>33.155</v>
+        <v>28.376</v>
       </c>
       <c r="Q14" t="n">
-        <v>35.207</v>
+        <v>30.077</v>
       </c>
       <c r="R14" t="n">
-        <v>40.802</v>
+        <v>34.971</v>
       </c>
       <c r="S14" t="n">
-        <v>51.181</v>
+        <v>44.262</v>
       </c>
       <c r="T14" t="n">
-        <v>64.05800000000001</v>
+        <v>56.171</v>
       </c>
       <c r="U14" t="n">
-        <v>86.792</v>
+        <v>77.262</v>
       </c>
       <c r="V14" t="n">
-        <v>88.523</v>
+        <v>79.761</v>
       </c>
       <c r="W14" t="n">
-        <v>85.852</v>
+        <v>77.94499999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>66.274</v>
+        <v>60.468</v>
       </c>
       <c r="Y14" t="n">
-        <v>55.908</v>
+        <v>51.245</v>
       </c>
     </row>
     <row r="15">
@@ -16985,76 +16985,76 @@
         <v>114</v>
       </c>
       <c r="B15" t="n">
-        <v>32.479</v>
+        <v>29.891</v>
       </c>
       <c r="C15" t="n">
-        <v>36.331</v>
+        <v>33.595</v>
       </c>
       <c r="D15" t="n">
-        <v>36.129</v>
+        <v>33.504</v>
       </c>
       <c r="E15" t="n">
-        <v>33.916</v>
+        <v>31.482</v>
       </c>
       <c r="F15" t="n">
-        <v>34.489</v>
+        <v>31.983</v>
       </c>
       <c r="G15" t="n">
-        <v>38.047</v>
+        <v>35.182</v>
       </c>
       <c r="H15" t="n">
-        <v>36.452</v>
+        <v>33.548</v>
       </c>
       <c r="I15" t="n">
-        <v>44.487</v>
+        <v>40.673</v>
       </c>
       <c r="J15" t="n">
-        <v>47.193</v>
+        <v>42.789</v>
       </c>
       <c r="K15" t="n">
-        <v>42.506</v>
+        <v>38.162</v>
       </c>
       <c r="L15" t="n">
-        <v>34.279</v>
+        <v>30.442</v>
       </c>
       <c r="M15" t="n">
-        <v>29.38</v>
+        <v>25.798</v>
       </c>
       <c r="N15" t="n">
-        <v>25.284</v>
+        <v>21.964</v>
       </c>
       <c r="O15" t="n">
-        <v>26.624</v>
+        <v>22.922</v>
       </c>
       <c r="P15" t="n">
-        <v>25.529</v>
+        <v>21.849</v>
       </c>
       <c r="Q15" t="n">
-        <v>26.159</v>
+        <v>22.347</v>
       </c>
       <c r="R15" t="n">
-        <v>28.87</v>
+        <v>24.744</v>
       </c>
       <c r="S15" t="n">
-        <v>38.593</v>
+        <v>33.376</v>
       </c>
       <c r="T15" t="n">
-        <v>49.446</v>
+        <v>43.358</v>
       </c>
       <c r="U15" t="n">
-        <v>61.062</v>
+        <v>54.357</v>
       </c>
       <c r="V15" t="n">
-        <v>64.068</v>
+        <v>57.727</v>
       </c>
       <c r="W15" t="n">
-        <v>60.899</v>
+        <v>55.29</v>
       </c>
       <c r="X15" t="n">
-        <v>47.205</v>
+        <v>43.069</v>
       </c>
       <c r="Y15" t="n">
-        <v>38.014</v>
+        <v>34.843</v>
       </c>
     </row>
     <row r="16">
@@ -17062,76 +17062,76 @@
         <v>115</v>
       </c>
       <c r="B16" t="n">
-        <v>79.136</v>
+        <v>72.831</v>
       </c>
       <c r="C16" t="n">
-        <v>105.477</v>
+        <v>97.535</v>
       </c>
       <c r="D16" t="n">
-        <v>129.397</v>
+        <v>119.996</v>
       </c>
       <c r="E16" t="n">
-        <v>120.417</v>
+        <v>111.775</v>
       </c>
       <c r="F16" t="n">
-        <v>115.541</v>
+        <v>107.146</v>
       </c>
       <c r="G16" t="n">
-        <v>103.644</v>
+        <v>95.84</v>
       </c>
       <c r="H16" t="n">
-        <v>80.45999999999999</v>
+        <v>74.04900000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>63.187</v>
+        <v>57.77</v>
       </c>
       <c r="J16" t="n">
-        <v>53.329</v>
+        <v>48.352</v>
       </c>
       <c r="K16" t="n">
-        <v>47.321</v>
+        <v>42.485</v>
       </c>
       <c r="L16" t="n">
-        <v>43.823</v>
+        <v>38.917</v>
       </c>
       <c r="M16" t="n">
-        <v>45.004</v>
+        <v>39.517</v>
       </c>
       <c r="N16" t="n">
-        <v>39.326</v>
+        <v>34.162</v>
       </c>
       <c r="O16" t="n">
-        <v>41.2</v>
+        <v>35.471</v>
       </c>
       <c r="P16" t="n">
-        <v>39.638</v>
+        <v>33.924</v>
       </c>
       <c r="Q16" t="n">
-        <v>37.396</v>
+        <v>31.947</v>
       </c>
       <c r="R16" t="n">
-        <v>39.08</v>
+        <v>33.495</v>
       </c>
       <c r="S16" t="n">
-        <v>38.732</v>
+        <v>33.496</v>
       </c>
       <c r="T16" t="n">
-        <v>39.822</v>
+        <v>34.919</v>
       </c>
       <c r="U16" t="n">
-        <v>44.455</v>
+        <v>39.574</v>
       </c>
       <c r="V16" t="n">
-        <v>52.025</v>
+        <v>46.875</v>
       </c>
       <c r="W16" t="n">
-        <v>56.611</v>
+        <v>51.397</v>
       </c>
       <c r="X16" t="n">
-        <v>74.36499999999999</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>77.08799999999999</v>
+        <v>70.65900000000001</v>
       </c>
     </row>
     <row r="17">
@@ -17139,76 +17139,76 @@
         <v>116</v>
       </c>
       <c r="B17" t="n">
-        <v>23.033</v>
+        <v>21.198</v>
       </c>
       <c r="C17" t="n">
-        <v>24.108</v>
+        <v>22.293</v>
       </c>
       <c r="D17" t="n">
-        <v>23.693</v>
+        <v>21.972</v>
       </c>
       <c r="E17" t="n">
-        <v>21.968</v>
+        <v>20.391</v>
       </c>
       <c r="F17" t="n">
-        <v>23.171</v>
+        <v>21.488</v>
       </c>
       <c r="G17" t="n">
-        <v>20.799</v>
+        <v>19.233</v>
       </c>
       <c r="H17" t="n">
-        <v>19.417</v>
+        <v>17.87</v>
       </c>
       <c r="I17" t="n">
-        <v>20.616</v>
+        <v>18.849</v>
       </c>
       <c r="J17" t="n">
-        <v>19.878</v>
+        <v>18.023</v>
       </c>
       <c r="K17" t="n">
-        <v>19.551</v>
+        <v>17.553</v>
       </c>
       <c r="L17" t="n">
-        <v>20.377</v>
+        <v>18.096</v>
       </c>
       <c r="M17" t="n">
-        <v>18.443</v>
+        <v>16.194</v>
       </c>
       <c r="N17" t="n">
-        <v>17.362</v>
+        <v>15.082</v>
       </c>
       <c r="O17" t="n">
-        <v>16.681</v>
+        <v>14.362</v>
       </c>
       <c r="P17" t="n">
-        <v>16.021</v>
+        <v>13.712</v>
       </c>
       <c r="Q17" t="n">
-        <v>15.891</v>
+        <v>13.575</v>
       </c>
       <c r="R17" t="n">
-        <v>16.337</v>
+        <v>14.002</v>
       </c>
       <c r="S17" t="n">
-        <v>16.229</v>
+        <v>14.035</v>
       </c>
       <c r="T17" t="n">
-        <v>17.489</v>
+        <v>15.335</v>
       </c>
       <c r="U17" t="n">
-        <v>19.338</v>
+        <v>17.215</v>
       </c>
       <c r="V17" t="n">
-        <v>19.883</v>
+        <v>17.915</v>
       </c>
       <c r="W17" t="n">
-        <v>20.276</v>
+        <v>18.409</v>
       </c>
       <c r="X17" t="n">
-        <v>21.217</v>
+        <v>19.358</v>
       </c>
       <c r="Y17" t="n">
-        <v>22.608</v>
+        <v>20.723</v>
       </c>
     </row>
     <row r="18">
@@ -17293,76 +17293,76 @@
         <v>118</v>
       </c>
       <c r="B19" t="n">
-        <v>84.95999999999999</v>
+        <v>78.191</v>
       </c>
       <c r="C19" t="n">
-        <v>78.268</v>
+        <v>72.374</v>
       </c>
       <c r="D19" t="n">
-        <v>80.629</v>
+        <v>74.771</v>
       </c>
       <c r="E19" t="n">
-        <v>83.17</v>
+        <v>77.20099999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>81.17</v>
+        <v>75.273</v>
       </c>
       <c r="G19" t="n">
-        <v>71.676</v>
+        <v>66.279</v>
       </c>
       <c r="H19" t="n">
-        <v>73.98999999999999</v>
+        <v>68.09399999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>70.654</v>
+        <v>64.596</v>
       </c>
       <c r="J19" t="n">
-        <v>66.974</v>
+        <v>60.724</v>
       </c>
       <c r="K19" t="n">
-        <v>65.746</v>
+        <v>59.027</v>
       </c>
       <c r="L19" t="n">
-        <v>69.01300000000001</v>
+        <v>61.287</v>
       </c>
       <c r="M19" t="n">
-        <v>61.47</v>
+        <v>53.975</v>
       </c>
       <c r="N19" t="n">
-        <v>62.509</v>
+        <v>54.301</v>
       </c>
       <c r="O19" t="n">
-        <v>59.975</v>
+        <v>51.636</v>
       </c>
       <c r="P19" t="n">
-        <v>54.394</v>
+        <v>46.553</v>
       </c>
       <c r="Q19" t="n">
-        <v>62.377</v>
+        <v>53.288</v>
       </c>
       <c r="R19" t="n">
-        <v>57.034</v>
+        <v>48.883</v>
       </c>
       <c r="S19" t="n">
-        <v>53.826</v>
+        <v>46.55</v>
       </c>
       <c r="T19" t="n">
-        <v>60.504</v>
+        <v>53.054</v>
       </c>
       <c r="U19" t="n">
-        <v>62.087</v>
+        <v>55.27</v>
       </c>
       <c r="V19" t="n">
-        <v>66.986</v>
+        <v>60.356</v>
       </c>
       <c r="W19" t="n">
-        <v>73.48</v>
+        <v>66.71299999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>75.218</v>
+        <v>68.628</v>
       </c>
       <c r="Y19" t="n">
-        <v>79.09099999999999</v>
+        <v>72.495</v>
       </c>
     </row>
     <row r="20">
@@ -17370,76 +17370,76 @@
         <v>119</v>
       </c>
       <c r="B20" t="n">
-        <v>24.343</v>
+        <v>22.403</v>
       </c>
       <c r="C20" t="n">
-        <v>24.267</v>
+        <v>22.44</v>
       </c>
       <c r="D20" t="n">
-        <v>26.818</v>
+        <v>24.87</v>
       </c>
       <c r="E20" t="n">
-        <v>26.17</v>
+        <v>24.291</v>
       </c>
       <c r="F20" t="n">
-        <v>25.364</v>
+        <v>23.522</v>
       </c>
       <c r="G20" t="n">
-        <v>26.781</v>
+        <v>24.765</v>
       </c>
       <c r="H20" t="n">
-        <v>25.463</v>
+        <v>23.434</v>
       </c>
       <c r="I20" t="n">
-        <v>26.093</v>
+        <v>23.856</v>
       </c>
       <c r="J20" t="n">
-        <v>32.006</v>
+        <v>29.019</v>
       </c>
       <c r="K20" t="n">
-        <v>34.137</v>
+        <v>30.648</v>
       </c>
       <c r="L20" t="n">
-        <v>47.503</v>
+        <v>42.185</v>
       </c>
       <c r="M20" t="n">
-        <v>50.541</v>
+        <v>44.379</v>
       </c>
       <c r="N20" t="n">
-        <v>54.291</v>
+        <v>47.162</v>
       </c>
       <c r="O20" t="n">
-        <v>62.81</v>
+        <v>54.077</v>
       </c>
       <c r="P20" t="n">
-        <v>53.718</v>
+        <v>45.974</v>
       </c>
       <c r="Q20" t="n">
-        <v>53.252</v>
+        <v>45.492</v>
       </c>
       <c r="R20" t="n">
-        <v>43.866</v>
+        <v>37.596</v>
       </c>
       <c r="S20" t="n">
-        <v>38.588</v>
+        <v>33.372</v>
       </c>
       <c r="T20" t="n">
-        <v>33.001</v>
+        <v>28.937</v>
       </c>
       <c r="U20" t="n">
-        <v>27.403</v>
+        <v>24.394</v>
       </c>
       <c r="V20" t="n">
-        <v>26.292</v>
+        <v>23.69</v>
       </c>
       <c r="W20" t="n">
-        <v>25.903</v>
+        <v>23.518</v>
       </c>
       <c r="X20" t="n">
-        <v>23.638</v>
+        <v>21.567</v>
       </c>
       <c r="Y20" t="n">
-        <v>22.862</v>
+        <v>20.955</v>
       </c>
     </row>
     <row r="21">
@@ -17447,76 +17447,76 @@
         <v>120</v>
       </c>
       <c r="B21" t="n">
-        <v>30.682</v>
+        <v>28.237</v>
       </c>
       <c r="C21" t="n">
-        <v>31.407</v>
+        <v>29.042</v>
       </c>
       <c r="D21" t="n">
-        <v>31.075</v>
+        <v>28.817</v>
       </c>
       <c r="E21" t="n">
-        <v>29.703</v>
+        <v>27.571</v>
       </c>
       <c r="F21" t="n">
-        <v>27.958</v>
+        <v>25.927</v>
       </c>
       <c r="G21" t="n">
-        <v>27.812</v>
+        <v>25.718</v>
       </c>
       <c r="H21" t="n">
-        <v>27.826</v>
+        <v>25.609</v>
       </c>
       <c r="I21" t="n">
-        <v>26.958</v>
+        <v>24.647</v>
       </c>
       <c r="J21" t="n">
-        <v>27.113</v>
+        <v>24.583</v>
       </c>
       <c r="K21" t="n">
-        <v>25.967</v>
+        <v>23.313</v>
       </c>
       <c r="L21" t="n">
-        <v>24.614</v>
+        <v>21.859</v>
       </c>
       <c r="M21" t="n">
-        <v>26.309</v>
+        <v>23.101</v>
       </c>
       <c r="N21" t="n">
-        <v>23.469</v>
+        <v>20.387</v>
       </c>
       <c r="O21" t="n">
-        <v>21.18</v>
+        <v>18.235</v>
       </c>
       <c r="P21" t="n">
-        <v>23.017</v>
+        <v>19.699</v>
       </c>
       <c r="Q21" t="n">
-        <v>21.318</v>
+        <v>18.212</v>
       </c>
       <c r="R21" t="n">
-        <v>21.466</v>
+        <v>18.398</v>
       </c>
       <c r="S21" t="n">
-        <v>20.922</v>
+        <v>18.093</v>
       </c>
       <c r="T21" t="n">
-        <v>25.453</v>
+        <v>22.319</v>
       </c>
       <c r="U21" t="n">
-        <v>22.936</v>
+        <v>20.418</v>
       </c>
       <c r="V21" t="n">
-        <v>24.307</v>
+        <v>21.901</v>
       </c>
       <c r="W21" t="n">
-        <v>26.524</v>
+        <v>24.081</v>
       </c>
       <c r="X21" t="n">
-        <v>29.352</v>
+        <v>26.78</v>
       </c>
       <c r="Y21" t="n">
-        <v>30.362</v>
+        <v>27.83</v>
       </c>
     </row>
     <row r="22">
@@ -17832,76 +17832,76 @@
         <v>201</v>
       </c>
       <c r="B26" t="n">
-        <v>19.18</v>
+        <v>17.652</v>
       </c>
       <c r="C26" t="n">
-        <v>19.614</v>
+        <v>18.137</v>
       </c>
       <c r="D26" t="n">
-        <v>20.185</v>
+        <v>18.719</v>
       </c>
       <c r="E26" t="n">
-        <v>18.942</v>
+        <v>17.582</v>
       </c>
       <c r="F26" t="n">
-        <v>18.756</v>
+        <v>17.393</v>
       </c>
       <c r="G26" t="n">
-        <v>19.842</v>
+        <v>18.348</v>
       </c>
       <c r="H26" t="n">
-        <v>22.828</v>
+        <v>21.009</v>
       </c>
       <c r="I26" t="n">
-        <v>24.626</v>
+        <v>22.514</v>
       </c>
       <c r="J26" t="n">
-        <v>26.995</v>
+        <v>24.476</v>
       </c>
       <c r="K26" t="n">
-        <v>23.641</v>
+        <v>21.225</v>
       </c>
       <c r="L26" t="n">
-        <v>20.222</v>
+        <v>17.958</v>
       </c>
       <c r="M26" t="n">
-        <v>16.752</v>
+        <v>14.709</v>
       </c>
       <c r="N26" t="n">
-        <v>14.602</v>
+        <v>12.685</v>
       </c>
       <c r="O26" t="n">
-        <v>14.352</v>
+        <v>12.356</v>
       </c>
       <c r="P26" t="n">
-        <v>13.444</v>
+        <v>11.506</v>
       </c>
       <c r="Q26" t="n">
-        <v>15.48</v>
+        <v>13.224</v>
       </c>
       <c r="R26" t="n">
-        <v>17.203</v>
+        <v>14.744</v>
       </c>
       <c r="S26" t="n">
-        <v>20.22</v>
+        <v>17.486</v>
       </c>
       <c r="T26" t="n">
-        <v>28.299</v>
+        <v>24.814</v>
       </c>
       <c r="U26" t="n">
-        <v>34.46</v>
+        <v>30.677</v>
       </c>
       <c r="V26" t="n">
-        <v>37.397</v>
+        <v>33.695</v>
       </c>
       <c r="W26" t="n">
-        <v>32.925</v>
+        <v>29.893</v>
       </c>
       <c r="X26" t="n">
-        <v>26.942</v>
+        <v>24.581</v>
       </c>
       <c r="Y26" t="n">
-        <v>21.65</v>
+        <v>19.845</v>
       </c>
     </row>
     <row r="27">
@@ -17909,76 +17909,76 @@
         <v>202</v>
       </c>
       <c r="B27" t="n">
-        <v>24.047</v>
+        <v>22.131</v>
       </c>
       <c r="C27" t="n">
-        <v>23.906</v>
+        <v>22.106</v>
       </c>
       <c r="D27" t="n">
-        <v>22.958</v>
+        <v>21.29</v>
       </c>
       <c r="E27" t="n">
-        <v>25.402</v>
+        <v>23.579</v>
       </c>
       <c r="F27" t="n">
-        <v>21.664</v>
+        <v>20.09</v>
       </c>
       <c r="G27" t="n">
-        <v>23.199</v>
+        <v>21.452</v>
       </c>
       <c r="H27" t="n">
-        <v>20.875</v>
+        <v>19.212</v>
       </c>
       <c r="I27" t="n">
-        <v>20.014</v>
+        <v>18.298</v>
       </c>
       <c r="J27" t="n">
-        <v>21.447</v>
+        <v>19.445</v>
       </c>
       <c r="K27" t="n">
-        <v>20.686</v>
+        <v>18.571</v>
       </c>
       <c r="L27" t="n">
-        <v>19.789</v>
+        <v>17.574</v>
       </c>
       <c r="M27" t="n">
-        <v>18.079</v>
+        <v>15.875</v>
       </c>
       <c r="N27" t="n">
-        <v>17.374</v>
+        <v>15.093</v>
       </c>
       <c r="O27" t="n">
-        <v>18.36</v>
+        <v>15.807</v>
       </c>
       <c r="P27" t="n">
-        <v>16.464</v>
+        <v>14.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>16.214</v>
+        <v>13.851</v>
       </c>
       <c r="R27" t="n">
-        <v>16.4</v>
+        <v>14.056</v>
       </c>
       <c r="S27" t="n">
-        <v>16.375</v>
+        <v>14.162</v>
       </c>
       <c r="T27" t="n">
-        <v>16.504</v>
+        <v>14.472</v>
       </c>
       <c r="U27" t="n">
-        <v>17.809</v>
+        <v>15.854</v>
       </c>
       <c r="V27" t="n">
-        <v>19.348</v>
+        <v>17.433</v>
       </c>
       <c r="W27" t="n">
-        <v>20.732</v>
+        <v>18.822</v>
       </c>
       <c r="X27" t="n">
-        <v>21.589</v>
+        <v>19.698</v>
       </c>
       <c r="Y27" t="n">
-        <v>23.115</v>
+        <v>21.187</v>
       </c>
     </row>
     <row r="28">
@@ -17986,76 +17986,76 @@
         <v>203</v>
       </c>
       <c r="B28" t="n">
-        <v>22.959</v>
+        <v>21.13</v>
       </c>
       <c r="C28" t="n">
-        <v>23.587</v>
+        <v>21.811</v>
       </c>
       <c r="D28" t="n">
-        <v>27.249</v>
+        <v>25.269</v>
       </c>
       <c r="E28" t="n">
-        <v>26.627</v>
+        <v>24.716</v>
       </c>
       <c r="F28" t="n">
-        <v>26.17</v>
+        <v>24.269</v>
       </c>
       <c r="G28" t="n">
-        <v>26.115</v>
+        <v>24.149</v>
       </c>
       <c r="H28" t="n">
-        <v>25.368</v>
+        <v>23.346</v>
       </c>
       <c r="I28" t="n">
-        <v>27.657</v>
+        <v>25.286</v>
       </c>
       <c r="J28" t="n">
-        <v>30.089</v>
+        <v>27.281</v>
       </c>
       <c r="K28" t="n">
-        <v>35.192</v>
+        <v>31.595</v>
       </c>
       <c r="L28" t="n">
-        <v>45.405</v>
+        <v>40.322</v>
       </c>
       <c r="M28" t="n">
-        <v>51.577</v>
+        <v>45.288</v>
       </c>
       <c r="N28" t="n">
-        <v>58.602</v>
+        <v>50.908</v>
       </c>
       <c r="O28" t="n">
-        <v>60.763</v>
+        <v>52.314</v>
       </c>
       <c r="P28" t="n">
-        <v>63.528</v>
+        <v>54.371</v>
       </c>
       <c r="Q28" t="n">
-        <v>55.415</v>
+        <v>47.34</v>
       </c>
       <c r="R28" t="n">
-        <v>46.665</v>
+        <v>39.996</v>
       </c>
       <c r="S28" t="n">
-        <v>40.736</v>
+        <v>35.229</v>
       </c>
       <c r="T28" t="n">
-        <v>33.087</v>
+        <v>29.013</v>
       </c>
       <c r="U28" t="n">
-        <v>26.404</v>
+        <v>23.505</v>
       </c>
       <c r="V28" t="n">
-        <v>27.183</v>
+        <v>24.492</v>
       </c>
       <c r="W28" t="n">
-        <v>23.884</v>
+        <v>21.684</v>
       </c>
       <c r="X28" t="n">
-        <v>24.804</v>
+        <v>22.631</v>
       </c>
       <c r="Y28" t="n">
-        <v>23.919</v>
+        <v>21.924</v>
       </c>
     </row>
     <row r="29">
@@ -18063,76 +18063,76 @@
         <v>204</v>
       </c>
       <c r="B29" t="n">
-        <v>10.478</v>
+        <v>9.643000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>10.829</v>
+        <v>10.013</v>
       </c>
       <c r="D29" t="n">
-        <v>9.974</v>
+        <v>9.249000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>10.278</v>
+        <v>9.541</v>
       </c>
       <c r="F29" t="n">
-        <v>9.722</v>
+        <v>9.015000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>10.723</v>
+        <v>9.916</v>
       </c>
       <c r="H29" t="n">
-        <v>10.683</v>
+        <v>9.831</v>
       </c>
       <c r="I29" t="n">
-        <v>11.423</v>
+        <v>10.443</v>
       </c>
       <c r="J29" t="n">
-        <v>12.607</v>
+        <v>11.431</v>
       </c>
       <c r="K29" t="n">
-        <v>14.225</v>
+        <v>12.772</v>
       </c>
       <c r="L29" t="n">
-        <v>15.902</v>
+        <v>14.122</v>
       </c>
       <c r="M29" t="n">
-        <v>20.094</v>
+        <v>17.644</v>
       </c>
       <c r="N29" t="n">
-        <v>23.305</v>
+        <v>20.245</v>
       </c>
       <c r="O29" t="n">
-        <v>22.624</v>
+        <v>19.478</v>
       </c>
       <c r="P29" t="n">
-        <v>24.285</v>
+        <v>20.785</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.875</v>
+        <v>18.688</v>
       </c>
       <c r="R29" t="n">
-        <v>19.226</v>
+        <v>16.478</v>
       </c>
       <c r="S29" t="n">
-        <v>16.286</v>
+        <v>14.084</v>
       </c>
       <c r="T29" t="n">
-        <v>12.935</v>
+        <v>11.342</v>
       </c>
       <c r="U29" t="n">
-        <v>11.919</v>
+        <v>10.61</v>
       </c>
       <c r="V29" t="n">
-        <v>10.568</v>
+        <v>9.522</v>
       </c>
       <c r="W29" t="n">
-        <v>10.794</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X29" t="n">
-        <v>9.340999999999999</v>
+        <v>8.522</v>
       </c>
       <c r="Y29" t="n">
-        <v>10.289</v>
+        <v>9.430999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -18140,76 +18140,76 @@
         <v>205</v>
       </c>
       <c r="B30" t="n">
-        <v>15.812</v>
+        <v>14.552</v>
       </c>
       <c r="C30" t="n">
-        <v>15.562</v>
+        <v>14.39</v>
       </c>
       <c r="D30" t="n">
-        <v>15.916</v>
+        <v>14.759</v>
       </c>
       <c r="E30" t="n">
-        <v>16.204</v>
+        <v>15.041</v>
       </c>
       <c r="F30" t="n">
-        <v>16.23</v>
+        <v>15.051</v>
       </c>
       <c r="G30" t="n">
-        <v>15.307</v>
+        <v>14.154</v>
       </c>
       <c r="H30" t="n">
-        <v>14.21</v>
+        <v>13.078</v>
       </c>
       <c r="I30" t="n">
-        <v>13.902</v>
+        <v>12.71</v>
       </c>
       <c r="J30" t="n">
-        <v>14.47</v>
+        <v>13.12</v>
       </c>
       <c r="K30" t="n">
-        <v>13.702</v>
+        <v>12.302</v>
       </c>
       <c r="L30" t="n">
-        <v>13.976</v>
+        <v>12.411</v>
       </c>
       <c r="M30" t="n">
-        <v>12.253</v>
+        <v>10.759</v>
       </c>
       <c r="N30" t="n">
-        <v>12.518</v>
+        <v>10.874</v>
       </c>
       <c r="O30" t="n">
-        <v>12.407</v>
+        <v>10.682</v>
       </c>
       <c r="P30" t="n">
-        <v>11.012</v>
+        <v>9.425000000000001</v>
       </c>
       <c r="Q30" t="n">
-        <v>10.381</v>
+        <v>8.869</v>
       </c>
       <c r="R30" t="n">
-        <v>11.477</v>
+        <v>9.837</v>
       </c>
       <c r="S30" t="n">
-        <v>10.82</v>
+        <v>9.358000000000001</v>
       </c>
       <c r="T30" t="n">
-        <v>11.916</v>
+        <v>10.449</v>
       </c>
       <c r="U30" t="n">
-        <v>13.103</v>
+        <v>11.664</v>
       </c>
       <c r="V30" t="n">
-        <v>13.281</v>
+        <v>11.967</v>
       </c>
       <c r="W30" t="n">
-        <v>13.959</v>
+        <v>12.673</v>
       </c>
       <c r="X30" t="n">
-        <v>14.698</v>
+        <v>13.411</v>
       </c>
       <c r="Y30" t="n">
-        <v>14.903</v>
+        <v>13.66</v>
       </c>
     </row>
     <row r="31">
@@ -18217,76 +18217,76 @@
         <v>206</v>
       </c>
       <c r="B31" t="n">
-        <v>36.237</v>
+        <v>33.35</v>
       </c>
       <c r="C31" t="n">
-        <v>45.502</v>
+        <v>42.076</v>
       </c>
       <c r="D31" t="n">
-        <v>54.128</v>
+        <v>50.196</v>
       </c>
       <c r="E31" t="n">
-        <v>59.376</v>
+        <v>55.115</v>
       </c>
       <c r="F31" t="n">
-        <v>55.234</v>
+        <v>51.221</v>
       </c>
       <c r="G31" t="n">
-        <v>45.78</v>
+        <v>42.333</v>
       </c>
       <c r="H31" t="n">
-        <v>36.806</v>
+        <v>33.874</v>
       </c>
       <c r="I31" t="n">
-        <v>27.395</v>
+        <v>25.047</v>
       </c>
       <c r="J31" t="n">
-        <v>22.53</v>
+        <v>20.427</v>
       </c>
       <c r="K31" t="n">
-        <v>22.137</v>
+        <v>19.875</v>
       </c>
       <c r="L31" t="n">
-        <v>18.416</v>
+        <v>16.354</v>
       </c>
       <c r="M31" t="n">
-        <v>18.93</v>
+        <v>16.622</v>
       </c>
       <c r="N31" t="n">
-        <v>18.607</v>
+        <v>16.164</v>
       </c>
       <c r="O31" t="n">
-        <v>16.055</v>
+        <v>13.823</v>
       </c>
       <c r="P31" t="n">
-        <v>18.273</v>
+        <v>15.639</v>
       </c>
       <c r="Q31" t="n">
-        <v>17.324</v>
+        <v>14.8</v>
       </c>
       <c r="R31" t="n">
-        <v>17.547</v>
+        <v>15.039</v>
       </c>
       <c r="S31" t="n">
-        <v>18.197</v>
+        <v>15.737</v>
       </c>
       <c r="T31" t="n">
-        <v>18.315</v>
+        <v>16.06</v>
       </c>
       <c r="U31" t="n">
-        <v>18.996</v>
+        <v>16.911</v>
       </c>
       <c r="V31" t="n">
-        <v>22.608</v>
+        <v>20.37</v>
       </c>
       <c r="W31" t="n">
-        <v>25.343</v>
+        <v>23.009</v>
       </c>
       <c r="X31" t="n">
-        <v>32.264</v>
+        <v>29.438</v>
       </c>
       <c r="Y31" t="n">
-        <v>33.229</v>
+        <v>30.458</v>
       </c>
     </row>
     <row r="32">
@@ -18294,76 +18294,76 @@
         <v>207</v>
       </c>
       <c r="B32" t="n">
-        <v>16.252</v>
+        <v>14.957</v>
       </c>
       <c r="C32" t="n">
-        <v>18.276</v>
+        <v>16.9</v>
       </c>
       <c r="D32" t="n">
-        <v>17.08</v>
+        <v>15.839</v>
       </c>
       <c r="E32" t="n">
-        <v>17.079</v>
+        <v>15.853</v>
       </c>
       <c r="F32" t="n">
-        <v>18.439</v>
+        <v>17.1</v>
       </c>
       <c r="G32" t="n">
-        <v>18.002</v>
+        <v>16.646</v>
       </c>
       <c r="H32" t="n">
-        <v>17.556</v>
+        <v>16.157</v>
       </c>
       <c r="I32" t="n">
-        <v>18.456</v>
+        <v>16.874</v>
       </c>
       <c r="J32" t="n">
-        <v>20.833</v>
+        <v>18.889</v>
       </c>
       <c r="K32" t="n">
-        <v>23.783</v>
+        <v>21.353</v>
       </c>
       <c r="L32" t="n">
-        <v>28.161</v>
+        <v>25.009</v>
       </c>
       <c r="M32" t="n">
-        <v>31.852</v>
+        <v>27.968</v>
       </c>
       <c r="N32" t="n">
-        <v>35.58</v>
+        <v>30.908</v>
       </c>
       <c r="O32" t="n">
-        <v>40.158</v>
+        <v>34.575</v>
       </c>
       <c r="P32" t="n">
-        <v>38.837</v>
+        <v>33.239</v>
       </c>
       <c r="Q32" t="n">
-        <v>34.949</v>
+        <v>29.857</v>
       </c>
       <c r="R32" t="n">
-        <v>31.913</v>
+        <v>27.352</v>
       </c>
       <c r="S32" t="n">
-        <v>26.546</v>
+        <v>22.958</v>
       </c>
       <c r="T32" t="n">
-        <v>24.005</v>
+        <v>21.049</v>
       </c>
       <c r="U32" t="n">
-        <v>17.897</v>
+        <v>15.932</v>
       </c>
       <c r="V32" t="n">
-        <v>17.034</v>
+        <v>15.348</v>
       </c>
       <c r="W32" t="n">
-        <v>17.002</v>
+        <v>15.436</v>
       </c>
       <c r="X32" t="n">
-        <v>17.187</v>
+        <v>15.681</v>
       </c>
       <c r="Y32" t="n">
-        <v>17.312</v>
+        <v>15.868</v>
       </c>
     </row>
     <row r="33">
@@ -18371,76 +18371,76 @@
         <v>208</v>
       </c>
       <c r="B33" t="n">
-        <v>22.219</v>
+        <v>20.448</v>
       </c>
       <c r="C33" t="n">
-        <v>24.048</v>
+        <v>22.237</v>
       </c>
       <c r="D33" t="n">
-        <v>24.851</v>
+        <v>23.045</v>
       </c>
       <c r="E33" t="n">
-        <v>24.086</v>
+        <v>22.357</v>
       </c>
       <c r="F33" t="n">
-        <v>24.733</v>
+        <v>22.936</v>
       </c>
       <c r="G33" t="n">
-        <v>24.751</v>
+        <v>22.887</v>
       </c>
       <c r="H33" t="n">
-        <v>24.703</v>
+        <v>22.735</v>
       </c>
       <c r="I33" t="n">
-        <v>25.901</v>
+        <v>23.68</v>
       </c>
       <c r="J33" t="n">
-        <v>30.879</v>
+        <v>27.997</v>
       </c>
       <c r="K33" t="n">
-        <v>33.817</v>
+        <v>30.361</v>
       </c>
       <c r="L33" t="n">
-        <v>41.248</v>
+        <v>36.63</v>
       </c>
       <c r="M33" t="n">
-        <v>48.033</v>
+        <v>42.176</v>
       </c>
       <c r="N33" t="n">
-        <v>57.497</v>
+        <v>49.948</v>
       </c>
       <c r="O33" t="n">
-        <v>60.27</v>
+        <v>51.89</v>
       </c>
       <c r="P33" t="n">
-        <v>59.585</v>
+        <v>50.996</v>
       </c>
       <c r="Q33" t="n">
-        <v>51.71</v>
+        <v>44.175</v>
       </c>
       <c r="R33" t="n">
-        <v>44.477</v>
+        <v>38.121</v>
       </c>
       <c r="S33" t="n">
-        <v>37.193</v>
+        <v>32.165</v>
       </c>
       <c r="T33" t="n">
-        <v>32.243</v>
+        <v>28.272</v>
       </c>
       <c r="U33" t="n">
-        <v>26.159</v>
+        <v>23.287</v>
       </c>
       <c r="V33" t="n">
-        <v>23.302</v>
+        <v>20.995</v>
       </c>
       <c r="W33" t="n">
-        <v>23.99</v>
+        <v>21.78</v>
       </c>
       <c r="X33" t="n">
-        <v>23.916</v>
+        <v>21.821</v>
       </c>
       <c r="Y33" t="n">
-        <v>22.921</v>
+        <v>21.01</v>
       </c>
     </row>
     <row r="34">
@@ -18448,76 +18448,76 @@
         <v>209</v>
       </c>
       <c r="B34" t="n">
-        <v>44.453</v>
+        <v>40.911</v>
       </c>
       <c r="C34" t="n">
-        <v>41.1</v>
+        <v>38.005</v>
       </c>
       <c r="D34" t="n">
-        <v>43.082</v>
+        <v>39.952</v>
       </c>
       <c r="E34" t="n">
-        <v>42.698</v>
+        <v>39.633</v>
       </c>
       <c r="F34" t="n">
-        <v>38.839</v>
+        <v>36.017</v>
       </c>
       <c r="G34" t="n">
-        <v>38.791</v>
+        <v>35.87</v>
       </c>
       <c r="H34" t="n">
-        <v>39.538</v>
+        <v>36.387</v>
       </c>
       <c r="I34" t="n">
-        <v>37.101</v>
+        <v>33.921</v>
       </c>
       <c r="J34" t="n">
-        <v>37.03</v>
+        <v>33.575</v>
       </c>
       <c r="K34" t="n">
-        <v>35.513</v>
+        <v>31.884</v>
       </c>
       <c r="L34" t="n">
-        <v>35.019</v>
+        <v>31.099</v>
       </c>
       <c r="M34" t="n">
-        <v>33.963</v>
+        <v>29.822</v>
       </c>
       <c r="N34" t="n">
-        <v>31.012</v>
+        <v>26.94</v>
       </c>
       <c r="O34" t="n">
-        <v>34.45</v>
+        <v>29.66</v>
       </c>
       <c r="P34" t="n">
-        <v>30.892</v>
+        <v>26.439</v>
       </c>
       <c r="Q34" t="n">
-        <v>27.792</v>
+        <v>23.743</v>
       </c>
       <c r="R34" t="n">
-        <v>28.618</v>
+        <v>24.528</v>
       </c>
       <c r="S34" t="n">
-        <v>29.317</v>
+        <v>25.354</v>
       </c>
       <c r="T34" t="n">
-        <v>30.953</v>
+        <v>27.142</v>
       </c>
       <c r="U34" t="n">
-        <v>33.203</v>
+        <v>29.557</v>
       </c>
       <c r="V34" t="n">
-        <v>35.492</v>
+        <v>31.979</v>
       </c>
       <c r="W34" t="n">
-        <v>38.446</v>
+        <v>34.905</v>
       </c>
       <c r="X34" t="n">
-        <v>40.249</v>
+        <v>36.723</v>
       </c>
       <c r="Y34" t="n">
-        <v>38.336</v>
+        <v>35.139</v>
       </c>
     </row>
     <row r="35">
@@ -18525,76 +18525,76 @@
         <v>210</v>
       </c>
       <c r="B35" t="n">
-        <v>34.76</v>
+        <v>31.99</v>
       </c>
       <c r="C35" t="n">
-        <v>32.663</v>
+        <v>30.203</v>
       </c>
       <c r="D35" t="n">
-        <v>33.242</v>
+        <v>30.827</v>
       </c>
       <c r="E35" t="n">
-        <v>36.416</v>
+        <v>33.803</v>
       </c>
       <c r="F35" t="n">
-        <v>35.353</v>
+        <v>32.785</v>
       </c>
       <c r="G35" t="n">
-        <v>35.796</v>
+        <v>33.1</v>
       </c>
       <c r="H35" t="n">
-        <v>42.579</v>
+        <v>39.186</v>
       </c>
       <c r="I35" t="n">
-        <v>47.37</v>
+        <v>43.309</v>
       </c>
       <c r="J35" t="n">
-        <v>45.244</v>
+        <v>41.022</v>
       </c>
       <c r="K35" t="n">
-        <v>42.491</v>
+        <v>38.149</v>
       </c>
       <c r="L35" t="n">
-        <v>33.066</v>
+        <v>29.364</v>
       </c>
       <c r="M35" t="n">
-        <v>30.422</v>
+        <v>26.712</v>
       </c>
       <c r="N35" t="n">
-        <v>25.822</v>
+        <v>22.431</v>
       </c>
       <c r="O35" t="n">
-        <v>25.276</v>
+        <v>21.762</v>
       </c>
       <c r="P35" t="n">
-        <v>23.852</v>
+        <v>20.414</v>
       </c>
       <c r="Q35" t="n">
-        <v>27.563</v>
+        <v>23.547</v>
       </c>
       <c r="R35" t="n">
-        <v>30.26</v>
+        <v>25.936</v>
       </c>
       <c r="S35" t="n">
-        <v>37.697</v>
+        <v>32.601</v>
       </c>
       <c r="T35" t="n">
-        <v>48.837</v>
+        <v>42.824</v>
       </c>
       <c r="U35" t="n">
-        <v>61.246</v>
+        <v>54.521</v>
       </c>
       <c r="V35" t="n">
-        <v>70.054</v>
+        <v>63.12</v>
       </c>
       <c r="W35" t="n">
-        <v>59.383</v>
+        <v>53.914</v>
       </c>
       <c r="X35" t="n">
-        <v>49.884</v>
+        <v>45.514</v>
       </c>
       <c r="Y35" t="n">
-        <v>41.609</v>
+        <v>38.139</v>
       </c>
     </row>
     <row r="36">
@@ -18756,76 +18756,76 @@
         <v>213</v>
       </c>
       <c r="B38" t="n">
-        <v>43.319</v>
+        <v>39.868</v>
       </c>
       <c r="C38" t="n">
-        <v>44.534</v>
+        <v>41.181</v>
       </c>
       <c r="D38" t="n">
-        <v>45.7</v>
+        <v>42.38</v>
       </c>
       <c r="E38" t="n">
-        <v>49.019</v>
+        <v>45.501</v>
       </c>
       <c r="F38" t="n">
-        <v>48.212</v>
+        <v>44.709</v>
       </c>
       <c r="G38" t="n">
-        <v>48.795</v>
+        <v>45.121</v>
       </c>
       <c r="H38" t="n">
-        <v>56.299</v>
+        <v>51.814</v>
       </c>
       <c r="I38" t="n">
-        <v>62.403</v>
+        <v>57.053</v>
       </c>
       <c r="J38" t="n">
-        <v>60.072</v>
+        <v>54.466</v>
       </c>
       <c r="K38" t="n">
-        <v>53.934</v>
+        <v>48.422</v>
       </c>
       <c r="L38" t="n">
-        <v>45.455</v>
+        <v>40.366</v>
       </c>
       <c r="M38" t="n">
-        <v>39.345</v>
+        <v>34.548</v>
       </c>
       <c r="N38" t="n">
-        <v>35.701</v>
+        <v>31.014</v>
       </c>
       <c r="O38" t="n">
-        <v>34.983</v>
+        <v>30.119</v>
       </c>
       <c r="P38" t="n">
-        <v>34.272</v>
+        <v>29.332</v>
       </c>
       <c r="Q38" t="n">
-        <v>36.789</v>
+        <v>31.429</v>
       </c>
       <c r="R38" t="n">
-        <v>42.068</v>
+        <v>36.055</v>
       </c>
       <c r="S38" t="n">
-        <v>49.854</v>
+        <v>43.115</v>
       </c>
       <c r="T38" t="n">
-        <v>68.914</v>
+        <v>60.429</v>
       </c>
       <c r="U38" t="n">
-        <v>88.036</v>
+        <v>78.37</v>
       </c>
       <c r="V38" t="n">
-        <v>93.654</v>
+        <v>84.384</v>
       </c>
       <c r="W38" t="n">
-        <v>82.71899999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="X38" t="n">
-        <v>67.246</v>
+        <v>61.355</v>
       </c>
       <c r="Y38" t="n">
-        <v>54.974</v>
+        <v>50.389</v>
       </c>
     </row>
     <row r="39">
@@ -18833,76 +18833,76 @@
         <v>214</v>
       </c>
       <c r="B39" t="n">
-        <v>44.502</v>
+        <v>40.956</v>
       </c>
       <c r="C39" t="n">
-        <v>45.08</v>
+        <v>41.686</v>
       </c>
       <c r="D39" t="n">
-        <v>48.075</v>
+        <v>44.582</v>
       </c>
       <c r="E39" t="n">
-        <v>44.215</v>
+        <v>41.042</v>
       </c>
       <c r="F39" t="n">
-        <v>43.703</v>
+        <v>40.528</v>
       </c>
       <c r="G39" t="n">
-        <v>42.365</v>
+        <v>39.175</v>
       </c>
       <c r="H39" t="n">
-        <v>44.454</v>
+        <v>40.912</v>
       </c>
       <c r="I39" t="n">
-        <v>38.684</v>
+        <v>35.367</v>
       </c>
       <c r="J39" t="n">
-        <v>36.437</v>
+        <v>33.037</v>
       </c>
       <c r="K39" t="n">
-        <v>39.377</v>
+        <v>35.352</v>
       </c>
       <c r="L39" t="n">
-        <v>35.225</v>
+        <v>31.281</v>
       </c>
       <c r="M39" t="n">
-        <v>36.094</v>
+        <v>31.693</v>
       </c>
       <c r="N39" t="n">
-        <v>37.396</v>
+        <v>32.486</v>
       </c>
       <c r="O39" t="n">
-        <v>37.204</v>
+        <v>32.031</v>
       </c>
       <c r="P39" t="n">
-        <v>33.98</v>
+        <v>29.082</v>
       </c>
       <c r="Q39" t="n">
-        <v>31.274</v>
+        <v>26.717</v>
       </c>
       <c r="R39" t="n">
-        <v>30.277</v>
+        <v>25.95</v>
       </c>
       <c r="S39" t="n">
-        <v>31.719</v>
+        <v>27.431</v>
       </c>
       <c r="T39" t="n">
-        <v>33.759</v>
+        <v>29.602</v>
       </c>
       <c r="U39" t="n">
-        <v>39.476</v>
+        <v>35.141</v>
       </c>
       <c r="V39" t="n">
-        <v>38.924</v>
+        <v>35.071</v>
       </c>
       <c r="W39" t="n">
-        <v>41.201</v>
+        <v>37.406</v>
       </c>
       <c r="X39" t="n">
-        <v>39.892</v>
+        <v>36.397</v>
       </c>
       <c r="Y39" t="n">
-        <v>46.797</v>
+        <v>42.894</v>
       </c>
     </row>
     <row r="40">
@@ -18910,76 +18910,76 @@
         <v>215</v>
       </c>
       <c r="B40" t="n">
-        <v>79.732</v>
+        <v>73.379</v>
       </c>
       <c r="C40" t="n">
-        <v>95.506</v>
+        <v>88.315</v>
       </c>
       <c r="D40" t="n">
-        <v>128.346</v>
+        <v>119.022</v>
       </c>
       <c r="E40" t="n">
-        <v>132.941</v>
+        <v>123.4</v>
       </c>
       <c r="F40" t="n">
-        <v>126.076</v>
+        <v>116.916</v>
       </c>
       <c r="G40" t="n">
-        <v>101.603</v>
+        <v>93.952</v>
       </c>
       <c r="H40" t="n">
-        <v>76.73699999999999</v>
+        <v>70.623</v>
       </c>
       <c r="I40" t="n">
-        <v>63.981</v>
+        <v>58.496</v>
       </c>
       <c r="J40" t="n">
-        <v>50.507</v>
+        <v>45.793</v>
       </c>
       <c r="K40" t="n">
-        <v>48.601</v>
+        <v>43.634</v>
       </c>
       <c r="L40" t="n">
-        <v>44.894</v>
+        <v>39.868</v>
       </c>
       <c r="M40" t="n">
-        <v>43.639</v>
+        <v>38.318</v>
       </c>
       <c r="N40" t="n">
-        <v>41.179</v>
+        <v>35.772</v>
       </c>
       <c r="O40" t="n">
-        <v>40.486</v>
+        <v>34.856</v>
       </c>
       <c r="P40" t="n">
-        <v>38.66</v>
+        <v>33.087</v>
       </c>
       <c r="Q40" t="n">
-        <v>36.122</v>
+        <v>30.859</v>
       </c>
       <c r="R40" t="n">
-        <v>39.996</v>
+        <v>34.28</v>
       </c>
       <c r="S40" t="n">
-        <v>40.02</v>
+        <v>34.61</v>
       </c>
       <c r="T40" t="n">
-        <v>43.212</v>
+        <v>37.891</v>
       </c>
       <c r="U40" t="n">
-        <v>42.196</v>
+        <v>37.563</v>
       </c>
       <c r="V40" t="n">
-        <v>52.377</v>
+        <v>47.193</v>
       </c>
       <c r="W40" t="n">
-        <v>57.588</v>
+        <v>52.284</v>
       </c>
       <c r="X40" t="n">
-        <v>66.054</v>
+        <v>60.267</v>
       </c>
       <c r="Y40" t="n">
-        <v>79.887</v>
+        <v>73.22499999999999</v>
       </c>
     </row>
     <row r="41">
@@ -18987,76 +18987,76 @@
         <v>216</v>
       </c>
       <c r="B41" t="n">
-        <v>25.099</v>
+        <v>23.099</v>
       </c>
       <c r="C41" t="n">
-        <v>33.257</v>
+        <v>30.753</v>
       </c>
       <c r="D41" t="n">
-        <v>42.148</v>
+        <v>39.086</v>
       </c>
       <c r="E41" t="n">
-        <v>40.464</v>
+        <v>37.56</v>
       </c>
       <c r="F41" t="n">
-        <v>40.887</v>
+        <v>37.917</v>
       </c>
       <c r="G41" t="n">
-        <v>34.244</v>
+        <v>31.665</v>
       </c>
       <c r="H41" t="n">
-        <v>23.997</v>
+        <v>22.085</v>
       </c>
       <c r="I41" t="n">
-        <v>18.865</v>
+        <v>17.247</v>
       </c>
       <c r="J41" t="n">
-        <v>17.174</v>
+        <v>15.571</v>
       </c>
       <c r="K41" t="n">
-        <v>15.674</v>
+        <v>14.072</v>
       </c>
       <c r="L41" t="n">
-        <v>14.3</v>
+        <v>12.699</v>
       </c>
       <c r="M41" t="n">
-        <v>14.116</v>
+        <v>12.395</v>
       </c>
       <c r="N41" t="n">
-        <v>12.863</v>
+        <v>11.174</v>
       </c>
       <c r="O41" t="n">
-        <v>12.322</v>
+        <v>10.609</v>
       </c>
       <c r="P41" t="n">
-        <v>12.274</v>
+        <v>10.505</v>
       </c>
       <c r="Q41" t="n">
-        <v>11.193</v>
+        <v>9.561999999999999</v>
       </c>
       <c r="R41" t="n">
-        <v>12.213</v>
+        <v>10.468</v>
       </c>
       <c r="S41" t="n">
-        <v>12.411</v>
+        <v>10.733</v>
       </c>
       <c r="T41" t="n">
-        <v>13.111</v>
+        <v>11.497</v>
       </c>
       <c r="U41" t="n">
-        <v>14.273</v>
+        <v>12.705</v>
       </c>
       <c r="V41" t="n">
-        <v>15.421</v>
+        <v>13.895</v>
       </c>
       <c r="W41" t="n">
-        <v>16.312</v>
+        <v>14.81</v>
       </c>
       <c r="X41" t="n">
-        <v>22.542</v>
+        <v>20.567</v>
       </c>
       <c r="Y41" t="n">
-        <v>23.801</v>
+        <v>21.816</v>
       </c>
     </row>
     <row r="42">
@@ -19141,76 +19141,76 @@
         <v>218</v>
       </c>
       <c r="B43" t="n">
-        <v>57.902</v>
+        <v>53.288</v>
       </c>
       <c r="C43" t="n">
-        <v>58.209</v>
+        <v>53.826</v>
       </c>
       <c r="D43" t="n">
-        <v>62.734</v>
+        <v>58.176</v>
       </c>
       <c r="E43" t="n">
-        <v>59.668</v>
+        <v>55.386</v>
       </c>
       <c r="F43" t="n">
-        <v>60.607</v>
+        <v>56.203</v>
       </c>
       <c r="G43" t="n">
-        <v>64.482</v>
+        <v>59.627</v>
       </c>
       <c r="H43" t="n">
-        <v>68.501</v>
+        <v>63.043</v>
       </c>
       <c r="I43" t="n">
-        <v>81.486</v>
+        <v>74.501</v>
       </c>
       <c r="J43" t="n">
-        <v>80.70699999999999</v>
+        <v>73.175</v>
       </c>
       <c r="K43" t="n">
-        <v>73.672</v>
+        <v>66.142</v>
       </c>
       <c r="L43" t="n">
-        <v>61.362</v>
+        <v>54.493</v>
       </c>
       <c r="M43" t="n">
-        <v>50.958</v>
+        <v>44.744</v>
       </c>
       <c r="N43" t="n">
-        <v>40.281</v>
+        <v>34.992</v>
       </c>
       <c r="O43" t="n">
-        <v>42.154</v>
+        <v>36.293</v>
       </c>
       <c r="P43" t="n">
-        <v>39.9</v>
+        <v>34.148</v>
       </c>
       <c r="Q43" t="n">
-        <v>45.324</v>
+        <v>38.72</v>
       </c>
       <c r="R43" t="n">
-        <v>50.252</v>
+        <v>43.07</v>
       </c>
       <c r="S43" t="n">
-        <v>65.63500000000001</v>
+        <v>56.763</v>
       </c>
       <c r="T43" t="n">
-        <v>90.649</v>
+        <v>79.488</v>
       </c>
       <c r="U43" t="n">
-        <v>109.422</v>
+        <v>97.408</v>
       </c>
       <c r="V43" t="n">
-        <v>115.068</v>
+        <v>103.678</v>
       </c>
       <c r="W43" t="n">
-        <v>102.794</v>
+        <v>93.327</v>
       </c>
       <c r="X43" t="n">
-        <v>81.908</v>
+        <v>74.732</v>
       </c>
       <c r="Y43" t="n">
-        <v>71.36199999999999</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="44">
@@ -19218,76 +19218,76 @@
         <v>219</v>
       </c>
       <c r="B44" t="n">
-        <v>47.401</v>
+        <v>43.625</v>
       </c>
       <c r="C44" t="n">
-        <v>61.584</v>
+        <v>56.947</v>
       </c>
       <c r="D44" t="n">
-        <v>71.208</v>
+        <v>66.035</v>
       </c>
       <c r="E44" t="n">
-        <v>81.40000000000001</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>69.502</v>
+        <v>64.452</v>
       </c>
       <c r="G44" t="n">
-        <v>65.623</v>
+        <v>60.682</v>
       </c>
       <c r="H44" t="n">
-        <v>47.951</v>
+        <v>44.131</v>
       </c>
       <c r="I44" t="n">
-        <v>36.528</v>
+        <v>33.397</v>
       </c>
       <c r="J44" t="n">
-        <v>29.62</v>
+        <v>26.856</v>
       </c>
       <c r="K44" t="n">
-        <v>28.515</v>
+        <v>25.601</v>
       </c>
       <c r="L44" t="n">
-        <v>24.411</v>
+        <v>21.678</v>
       </c>
       <c r="M44" t="n">
-        <v>26.658</v>
+        <v>23.407</v>
       </c>
       <c r="N44" t="n">
-        <v>21.938</v>
+        <v>19.057</v>
       </c>
       <c r="O44" t="n">
-        <v>24.931</v>
+        <v>21.464</v>
       </c>
       <c r="P44" t="n">
-        <v>23.288</v>
+        <v>19.931</v>
       </c>
       <c r="Q44" t="n">
-        <v>20.207</v>
+        <v>17.262</v>
       </c>
       <c r="R44" t="n">
-        <v>22.985</v>
+        <v>19.7</v>
       </c>
       <c r="S44" t="n">
-        <v>23.358</v>
+        <v>20.201</v>
       </c>
       <c r="T44" t="n">
-        <v>23.372</v>
+        <v>20.495</v>
       </c>
       <c r="U44" t="n">
-        <v>25.796</v>
+        <v>22.963</v>
       </c>
       <c r="V44" t="n">
-        <v>30.172</v>
+        <v>27.186</v>
       </c>
       <c r="W44" t="n">
-        <v>35.231</v>
+        <v>31.986</v>
       </c>
       <c r="X44" t="n">
-        <v>37.162</v>
+        <v>33.906</v>
       </c>
       <c r="Y44" t="n">
-        <v>46.047</v>
+        <v>42.207</v>
       </c>
     </row>
     <row r="45">
@@ -19295,76 +19295,76 @@
         <v>220</v>
       </c>
       <c r="B45" t="n">
-        <v>33.846</v>
+        <v>31.149</v>
       </c>
       <c r="C45" t="n">
-        <v>44.998</v>
+        <v>41.609</v>
       </c>
       <c r="D45" t="n">
-        <v>51.264</v>
+        <v>47.539</v>
       </c>
       <c r="E45" t="n">
-        <v>55.508</v>
+        <v>51.48</v>
       </c>
       <c r="F45" t="n">
-        <v>50.833</v>
+        <v>47.14</v>
       </c>
       <c r="G45" t="n">
-        <v>41.276</v>
+        <v>38.168</v>
       </c>
       <c r="H45" t="n">
-        <v>33.553</v>
+        <v>30.88</v>
       </c>
       <c r="I45" t="n">
-        <v>26.207</v>
+        <v>23.96</v>
       </c>
       <c r="J45" t="n">
-        <v>21.251</v>
+        <v>19.268</v>
       </c>
       <c r="K45" t="n">
-        <v>19.778</v>
+        <v>17.757</v>
       </c>
       <c r="L45" t="n">
-        <v>19.006</v>
+        <v>16.879</v>
       </c>
       <c r="M45" t="n">
-        <v>18.331</v>
+        <v>16.096</v>
       </c>
       <c r="N45" t="n">
-        <v>16.303</v>
+        <v>14.163</v>
       </c>
       <c r="O45" t="n">
-        <v>15.753</v>
+        <v>13.562</v>
       </c>
       <c r="P45" t="n">
-        <v>15.907</v>
+        <v>13.614</v>
       </c>
       <c r="Q45" t="n">
-        <v>15.414</v>
+        <v>13.168</v>
       </c>
       <c r="R45" t="n">
-        <v>15.717</v>
+        <v>13.471</v>
       </c>
       <c r="S45" t="n">
-        <v>15.937</v>
+        <v>13.783</v>
       </c>
       <c r="T45" t="n">
-        <v>16.709</v>
+        <v>14.651</v>
       </c>
       <c r="U45" t="n">
-        <v>17.542</v>
+        <v>15.616</v>
       </c>
       <c r="V45" t="n">
-        <v>21.187</v>
+        <v>19.09</v>
       </c>
       <c r="W45" t="n">
-        <v>23.128</v>
+        <v>20.998</v>
       </c>
       <c r="X45" t="n">
-        <v>29.843</v>
+        <v>27.229</v>
       </c>
       <c r="Y45" t="n">
-        <v>33.574</v>
+        <v>30.774</v>
       </c>
     </row>
     <row r="46">
